--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,52 +25781,50 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>6.13</v>
+        <v>81.84</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0016</v>
+        <v>0.0027</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>8730000</v>
+        <v>11800000</v>
       </c>
       <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>61.01</v>
+        <v>45.85</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
       <c r="I583" s="6" t="inlineStr"/>
       <c r="J583" s="6" t="inlineStr"/>
-      <c r="K583" s="6" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
+      <c r="K583" s="6" t="inlineStr"/>
       <c r="L583" s="6" t="inlineStr"/>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>197.4</v>
+        <v>251</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0346</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>20610000</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>45.87</v>
+        <v>46.72</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25834,36 +25832,30 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L584" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L584" s="2" t="inlineStr"/>
       <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0346</v>
+        <v>0.0236</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E585" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>46.72</v>
+        <v>60.59</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25871,31 +25863,33 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>16.08</v>
+        <v>18.99</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0111</v>
+        <v>-0.0495</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>72700000</v>
+        <v>102290000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
-      <c r="F586" s="3" t="n">
-        <v>51.02</v>
-      </c>
+      <c r="F586" s="2" t="inlineStr"/>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="2" t="inlineStr"/>
@@ -25907,7 +25901,7 @@
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25915,106 +25909,110 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>4.73</v>
+        <v>80.95</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0216</v>
+        <v>0.0247</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>62450000</v>
+        <v>32400</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.58</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>77.90000000000001</v>
+        <v>41.16</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr"/>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>80.95</v>
+        <v>197.4</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0247</v>
+        <v>-0.099</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>32400</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>20610000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>41.16</v>
+        <v>45.87</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J588" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>18.99</v>
+        <v>62.95</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0495</v>
+        <v>-0.0008</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>102290000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
-      <c r="F589" s="6" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
+      <c r="F589" s="7" t="n">
+        <v>56.09</v>
+      </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
+      <c r="J589" s="8" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26022,34 +26020,38 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>2.82</v>
+        <v>10.56</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0537</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>52.07</v>
+        <v>53.86</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26057,40 +26059,34 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>2.74</v>
+        <v>13.89</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.0102</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>43.27</v>
+        <v>54.23</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26133,122 +26129,124 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>24.62</v>
+        <v>7.59</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>477650</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>56.05</v>
+        <v>39.58</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
+      <c r="I593" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J593" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr"/>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>81.84</v>
+        <v>24.62</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>11800000</v>
+        <v>15600000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>45.85</v>
+        <v>56.05</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="2" t="inlineStr"/>
       <c r="J594" s="2" t="inlineStr"/>
-      <c r="K594" s="2" t="inlineStr"/>
-      <c r="L594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>62.95</v>
+        <v>103.5</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>539710</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
-      <c r="F595" s="7" t="n">
-        <v>56.09</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
+      <c r="F595" s="6" t="inlineStr"/>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>13.89</v>
+        <v>4.73</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0102</v>
+        <v>0.0216</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>35540000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>62450000</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>54.23</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26256,12 +26254,12 @@
       <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26269,21 +26267,21 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>39.64</v>
+        <v>2.82</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.0537</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>12770000</v>
+        <v>263430000</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>52.02</v>
+        <v>52.07</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
@@ -26291,12 +26289,12 @@
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26304,38 +26302,40 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>10.56</v>
+        <v>2.74</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.08529999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>255670000</v>
+        <v>98340000</v>
       </c>
       <c r="E598" s="4" t="n">
-        <v>0.2479</v>
+        <v>0.7119</v>
       </c>
       <c r="F598" s="3" t="n">
-        <v>53.86</v>
+        <v>43.27</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="4" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="J598" s="2" t="inlineStr"/>
+        <v>-191.6342</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26343,21 +26343,21 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>33.9</v>
+        <v>16.08</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0174</v>
+        <v>-0.0111</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>4590000</v>
+        <v>72700000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>54.07</v>
+        <v>51.02</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26365,12 +26365,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26378,42 +26378,40 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>17.32</v>
+        <v>152.1</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0225</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>12210000</v>
+        <v>2330000</v>
       </c>
       <c r="E600" s="4" t="n">
-        <v>0.9246</v>
+        <v>0.1071</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G600" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>52.17</v>
+      </c>
+      <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
       <c r="I600" s="4" t="n">
-        <v>0.0028</v>
+        <v>-3.6635</v>
       </c>
       <c r="J600" s="4" t="n">
-        <v>-10.3171</v>
+        <v>-0.4897</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26421,110 +26419,108 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>6.95</v>
+        <v>6.13</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0016</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>78.58</v>
+        <v>61.01</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
         </is>
       </c>
-      <c r="L601" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="L601" s="6" t="inlineStr"/>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>103.5</v>
+        <v>28.66</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.001</v>
+        <v>-0.0478</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>398550</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
-      <c r="F602" s="2" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="F602" s="3" t="n">
+        <v>50.42</v>
+      </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>152.1</v>
+        <v>6.95</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0225</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>2330000</v>
+        <v>75580000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.1672</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>52.17</v>
+        <v>78.58</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
       <c r="I603" s="8" t="n">
-        <v>-3.6635</v>
+        <v>-5.3262</v>
       </c>
       <c r="J603" s="8" t="n">
-        <v>-0.4897</v>
+        <v>-4.2562</v>
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26532,21 +26528,21 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0595</v>
+        <v>-0.0174</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>14880000</v>
+        <v>4590000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>61.35</v>
+        <v>54.07</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26554,12 +26550,12 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26567,21 +26563,21 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>169</v>
+        <v>39.64</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0236</v>
+        <v>0.0195</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>12070000</v>
+        <v>12770000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>60.59</v>
+        <v>52.02</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26589,7 +26585,7 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
@@ -26602,36 +26598,42 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>28.66</v>
+        <v>17.32</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0478</v>
+        <v>0.0058</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>18930000</v>
+        <v>12210000</v>
       </c>
       <c r="E606" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.9246</v>
       </c>
       <c r="F606" s="3" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G606" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G606" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26639,38 +26641,36 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>7.59</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>14880000</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>39.58</v>
+        <v>61.35</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 07:30</t>
+          <t>23.04.2026 08:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,94 +25781,116 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>81.84</v>
+        <v>39.64</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0027</v>
+        <v>0.0195</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>11800000</v>
+        <v>12770000</v>
       </c>
       <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>45.85</v>
+        <v>52.02</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
       <c r="I583" s="6" t="inlineStr"/>
       <c r="J583" s="6" t="inlineStr"/>
-      <c r="K583" s="6" t="inlineStr"/>
-      <c r="L583" s="6" t="inlineStr"/>
+      <c r="K583" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>251</v>
+        <v>2.74</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0108</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>8590</v>
+        <v>98340000</v>
       </c>
       <c r="E584" s="4" t="n">
-        <v>0.2578</v>
+        <v>0.7119</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>46.72</v>
+        <v>43.27</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="2" t="inlineStr"/>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="I584" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J584" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L584" s="2" t="inlineStr"/>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
+      <c r="L584" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>169</v>
+        <v>6.95</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0236</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E585" s="6" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E585" s="8" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F585" s="7" t="n">
-        <v>60.59</v>
+        <v>78.58</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="6" t="inlineStr"/>
+      <c r="I585" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J585" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25876,32 +25898,40 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>18.99</v>
+        <v>152.1</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0495</v>
+        <v>-0.0225</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>102290000</v>
-      </c>
-      <c r="E586" s="2" t="inlineStr"/>
-      <c r="F586" s="2" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E586" s="4" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="F586" s="3" t="n">
+        <v>52.17</v>
+      </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="2" t="inlineStr"/>
-      <c r="J586" s="2" t="inlineStr"/>
+      <c r="I586" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J586" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25909,58 +25939,58 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>80.95</v>
+        <v>4.73</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0216</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>32400</v>
+        <v>62450000</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.58</v>
+        <v>0.8667</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>41.16</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>197.4</v>
+        <v>16.08</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0111</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>20610000</v>
+        <v>72700000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>45.87</v>
+        <v>51.02</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25968,12 +25998,12 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26020,60 +26050,58 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>10.56</v>
+        <v>7.59</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.08529999999999999</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>255670000</v>
+        <v>477650</v>
       </c>
       <c r="E590" s="4" t="n">
-        <v>0.2479</v>
+        <v>0.95</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>53.86</v>
+        <v>39.58</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
       <c r="I590" s="4" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="J590" s="2" t="inlineStr"/>
+        <v>-23.6291</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>13.89</v>
+        <v>41.38</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.0222</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>35540000</v>
+        <v>10990000</v>
       </c>
       <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>54.23</v>
+        <v>60.95</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
@@ -26081,12 +26109,12 @@
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26094,21 +26122,21 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>41.38</v>
+        <v>197.4</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0222</v>
+        <v>-0.099</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>10990000</v>
+        <v>20610000</v>
       </c>
       <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>60.95</v>
+        <v>45.87</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26116,12 +26144,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26129,38 +26157,36 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>7.59</v>
+        <v>169</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.0236</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E593" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>39.58</v>
+        <v>60.59</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J593" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I593" s="6" t="inlineStr"/>
+      <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
@@ -26201,52 +26227,56 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>103.5</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.001</v>
+        <v>-0.0595</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>398550</v>
+        <v>14880000</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
-      <c r="F595" s="6" t="inlineStr"/>
+      <c r="F595" s="7" t="n">
+        <v>61.35</v>
+      </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>4.73</v>
+        <v>2.82</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0216</v>
+        <v>-0.0537</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>263430000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>52.07</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26259,7 +26289,7 @@
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26267,34 +26297,38 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>2.82</v>
+        <v>10.56</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0537</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>52.07</v>
+        <v>53.86</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26302,62 +26336,48 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>2.74</v>
+        <v>81.84</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0108</v>
+        <v>0.0027</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E598" s="4" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>11800000</v>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>43.27</v>
+        <v>45.85</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J598" s="4" t="n">
-        <v>-0.8093</v>
-      </c>
-      <c r="K598" s="2" t="inlineStr">
-        <is>
-          <t>Dağıtım servisleri</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+      <c r="I598" s="2" t="inlineStr"/>
+      <c r="J598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>16.08</v>
+        <v>13.89</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0111</v>
+        <v>0.0102</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>72700000</v>
+        <v>35540000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>51.02</v>
+        <v>54.23</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26365,12 +26385,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26378,40 +26398,34 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>152.1</v>
+        <v>33.9</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0225</v>
+        <v>-0.0174</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>4590000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>52.17</v>
+        <v>54.07</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26419,22 +26433,20 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>6.13</v>
+        <v>18.99</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0495</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>8730000</v>
+        <v>102290000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="7" t="n">
-        <v>61.01</v>
-      </c>
+      <c r="F601" s="6" t="inlineStr"/>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
@@ -26444,42 +26456,52 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L601" s="6" t="inlineStr"/>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>28.66</v>
+        <v>17.32</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0478</v>
+        <v>0.0058</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>18930000</v>
+        <v>12210000</v>
       </c>
       <c r="E602" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.9246</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G602" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G602" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26487,40 +26509,36 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>6.95</v>
+        <v>28.66</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0478</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>75580000</v>
+        <v>18930000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.2667</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>78.58</v>
+        <v>50.42</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26528,21 +26546,23 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>33.9</v>
+        <v>251</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0346</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>4590000</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>54.07</v>
+        <v>46.72</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26550,112 +26570,96 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>39.64</v>
+        <v>103.5</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.001</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>12770000</v>
+        <v>398550</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
-      <c r="F605" s="7" t="n">
-        <v>52.02</v>
-      </c>
+      <c r="F605" s="6" t="inlineStr"/>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L605" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L605" s="6" t="inlineStr"/>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>17.32</v>
+        <v>80.95</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0247</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>12210000</v>
+        <v>32400</v>
       </c>
       <c r="E606" s="4" t="n">
-        <v>0.9246</v>
+        <v>0.58</v>
       </c>
       <c r="F606" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G606" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>41.16</v>
+      </c>
+      <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
       <c r="I606" s="4" t="n">
-        <v>0.0028</v>
+        <v>-9.409700000000001</v>
       </c>
       <c r="J606" s="4" t="n">
-        <v>-10.3171</v>
+        <v>-4.155</v>
       </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr"/>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>90.84999999999999</v>
+        <v>6.13</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0595</v>
+        <v>0.0016</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>14880000</v>
+        <v>8730000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>61.35</v>
+        <v>61.01</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
@@ -26663,14 +26667,10 @@
       <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 08:30</t>
+          <t>23.04.2026 09:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,75 +25781,77 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>39.64</v>
+        <v>7.59</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>12770000</v>
-      </c>
-      <c r="E583" s="6" t="inlineStr"/>
+        <v>477650</v>
+      </c>
+      <c r="E583" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F583" s="7" t="n">
-        <v>52.02</v>
+        <v>39.58</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
+      <c r="I583" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J583" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr"/>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>2.74</v>
+        <v>6.95</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0108</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>98340000</v>
+        <v>75580000</v>
       </c>
       <c r="E584" s="4" t="n">
-        <v>0.7119</v>
+        <v>0.1672</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>43.27</v>
+        <v>78.58</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
       <c r="I584" s="4" t="n">
-        <v>-191.6342</v>
+        <v>-5.3262</v>
       </c>
       <c r="J584" s="4" t="n">
-        <v>-0.8093</v>
+        <v>-4.2562</v>
       </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25857,40 +25859,38 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>6.95</v>
+        <v>62.95</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0008</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>75580000</v>
+        <v>539710</v>
       </c>
       <c r="E585" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F585" s="7" t="n">
-        <v>78.58</v>
+        <v>56.09</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
+      <c r="I585" s="6" t="inlineStr"/>
       <c r="J585" s="8" t="n">
-        <v>-4.2562</v>
+        <v>0.4139</v>
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25898,40 +25898,36 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>152.1</v>
+        <v>4.73</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0225</v>
+        <v>0.0216</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>2330000</v>
+        <v>62450000</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>0.1071</v>
+        <v>0.8667</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>52.17</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J586" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25939,23 +25935,21 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>4.73</v>
+        <v>169</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0216</v>
+        <v>0.0236</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>77.90000000000001</v>
+        <v>60.59</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25963,12 +25957,12 @@
       <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25976,145 +25970,137 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>16.08</v>
+        <v>81.84</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0111</v>
+        <v>0.0027</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>72700000</v>
+        <v>11800000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>51.02</v>
+        <v>45.85</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr"/>
       <c r="J588" s="2" t="inlineStr"/>
-      <c r="K588" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>62.95</v>
+        <v>80.95</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0008</v>
+        <v>0.0247</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>539710</v>
+        <v>32400</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>56.09</v>
+        <v>41.16</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="6" t="inlineStr"/>
+      <c r="I589" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
       <c r="J589" s="8" t="n">
-        <v>0.4139</v>
+        <v>-4.155</v>
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr"/>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>7.59</v>
+        <v>2.82</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0537</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>263430000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>39.58</v>
+        <v>52.07</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>41.38</v>
+        <v>10.56</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0222</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>10990000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>60.95</v>
+        <v>53.86</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26122,21 +26108,23 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>197.4</v>
+        <v>28.66</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0478</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>20610000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>45.87</v>
+        <v>50.42</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26149,7 +26137,7 @@
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26157,21 +26145,23 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0236</v>
+        <v>-0.0346</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>60.59</v>
+        <v>46.72</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26179,34 +26169,30 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr"/>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>24.62</v>
+        <v>197.4</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.099</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>15600000</v>
+        <v>20610000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>56.05</v>
+        <v>45.87</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26214,12 +26200,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26227,21 +26213,21 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>90.84999999999999</v>
+        <v>41.38</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0595</v>
+        <v>0.0222</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>14880000</v>
+        <v>10990000</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>61.35</v>
+        <v>60.95</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
@@ -26249,12 +26235,12 @@
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26262,21 +26248,21 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>2.82</v>
+        <v>33.9</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.0174</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>263430000</v>
+        <v>4590000</v>
       </c>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>52.07</v>
+        <v>54.07</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26284,12 +26270,12 @@
       <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26297,38 +26283,42 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>10.56</v>
+        <v>17.32</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>255670000</v>
+        <v>12210000</v>
       </c>
       <c r="E597" s="8" t="n">
-        <v>0.2479</v>
+        <v>0.9246</v>
       </c>
       <c r="F597" s="7" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="G597" s="6" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G597" s="7" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="J597" s="6" t="inlineStr"/>
+        <v>0.0028</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26336,48 +26326,56 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>81.84</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0595</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>11800000</v>
+        <v>14880000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>45.85</v>
+        <v>61.35</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="2" t="inlineStr"/>
       <c r="J598" s="2" t="inlineStr"/>
-      <c r="K598" s="2" t="inlineStr"/>
-      <c r="L598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>13.89</v>
+        <v>39.64</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.0195</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>35540000</v>
+        <v>12770000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>54.23</v>
+        <v>52.02</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26385,12 +26383,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26398,21 +26396,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>33.9</v>
+        <v>24.62</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0174</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>4590000</v>
+        <v>15600000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>54.07</v>
+        <v>56.05</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26420,12 +26418,12 @@
       <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26433,32 +26431,34 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>18.99</v>
+        <v>13.89</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0495</v>
+        <v>0.0102</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>102290000</v>
+        <v>35540000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="6" t="inlineStr"/>
+      <c r="F601" s="7" t="n">
+        <v>54.23</v>
+      </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26466,42 +26466,32 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>17.32</v>
+        <v>18.99</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0495</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.9246</v>
-      </c>
-      <c r="F602" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G602" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>102290000</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
+      <c r="F602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J602" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I602" s="2" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26509,36 +26499,40 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>28.66</v>
+        <v>2.74</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0478</v>
+        <v>-0.0108</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>18930000</v>
+        <v>98340000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.7119</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>50.42</v>
+        <v>43.27</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26546,31 +26540,27 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>251</v>
+        <v>103.5</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.001</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.2578</v>
-      </c>
-      <c r="F604" s="3" t="n">
-        <v>46.72</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
+      <c r="F604" s="2" t="inlineStr"/>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
       <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr"/>
@@ -26579,20 +26569,22 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>103.5</v>
+        <v>16.08</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.001</v>
+        <v>-0.0111</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>398550</v>
+        <v>72700000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
-      <c r="F605" s="6" t="inlineStr"/>
+      <c r="F605" s="7" t="n">
+        <v>51.02</v>
+      </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
@@ -26602,41 +26594,39 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L605" s="6" t="inlineStr"/>
+      <c r="L605" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>80.95</v>
+        <v>6.13</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0247</v>
+        <v>0.0016</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>32400</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>41.16</v>
+        <v>61.01</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J606" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr"/>
@@ -26645,32 +26635,42 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>6.13</v>
+        <v>152.1</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0225</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>8730000</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F607" s="7" t="n">
-        <v>61.01</v>
+        <v>52.17</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr"/>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 09:30</t>
+          <t>23.04.2026 10:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,77 +25781,67 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>7.59</v>
+        <v>18.99</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0495</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E583" s="8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F583" s="7" t="n">
-        <v>39.58</v>
-      </c>
+        <v>102290000</v>
+      </c>
+      <c r="E583" s="6" t="inlineStr"/>
+      <c r="F583" s="6" t="inlineStr"/>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J583" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>6.95</v>
+        <v>169</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0236</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E584" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>78.58</v>
+        <v>60.59</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J584" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I584" s="2" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25859,75 +25849,71 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>62.95</v>
+        <v>6.13</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0008</v>
+        <v>0.0016</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>539710</v>
-      </c>
-      <c r="E585" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>56.09</v>
+        <v>61.01</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
       <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr"/>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>4.73</v>
+        <v>2.74</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0216</v>
+        <v>-0.0108</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>62450000</v>
+        <v>98340000</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.7119</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>43.27</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="2" t="inlineStr"/>
-      <c r="J586" s="2" t="inlineStr"/>
+      <c r="I586" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J586" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25935,133 +25921,151 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>169</v>
+        <v>7.59</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0236</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E587" s="6" t="inlineStr"/>
+        <v>477650</v>
+      </c>
+      <c r="E587" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F587" s="7" t="n">
-        <v>60.59</v>
+        <v>39.58</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr"/>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>81.84</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0595</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>11800000</v>
+        <v>14880000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>45.85</v>
+        <v>61.35</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr"/>
       <c r="J588" s="2" t="inlineStr"/>
-      <c r="K588" s="2" t="inlineStr"/>
-      <c r="L588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>80.95</v>
+        <v>6.95</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0247</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>32400</v>
+        <v>75580000</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.58</v>
+        <v>0.1672</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>41.16</v>
+        <v>78.58</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="8" t="n">
-        <v>-9.409700000000001</v>
+        <v>-5.3262</v>
       </c>
       <c r="J589" s="8" t="n">
-        <v>-4.155</v>
+        <v>-4.2562</v>
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>2.82</v>
+        <v>62.95</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.0008</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>52.07</v>
+        <v>56.09</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
       <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="J590" s="4" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26069,38 +26073,34 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>10.56</v>
+        <v>13.89</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>255670000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.2479</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>53.86</v>
+        <v>54.23</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26145,23 +26145,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>251</v>
+        <v>39.64</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0346</v>
+        <v>0.0195</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E593" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>12770000</v>
+      </c>
+      <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>46.72</v>
+        <v>52.02</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26169,30 +26167,34 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>197.4</v>
+        <v>24.62</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.099</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>20610000</v>
+        <v>15600000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>45.87</v>
+        <v>56.05</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26200,12 +26202,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26213,21 +26215,21 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>41.38</v>
+        <v>2.82</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0222</v>
+        <v>-0.0537</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>10990000</v>
+        <v>263430000</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>60.95</v>
+        <v>52.07</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
@@ -26235,12 +26237,12 @@
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26248,34 +26250,40 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>33.9</v>
+        <v>152.1</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0225</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>4590000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>54.07</v>
+        <v>52.17</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J596" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26283,42 +26291,34 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>17.32</v>
+        <v>197.4</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0058</v>
+        <v>-0.099</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="E597" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>20610000</v>
+      </c>
+      <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G597" s="7" t="n">
-        <v>163.71</v>
-      </c>
+        <v>45.87</v>
+      </c>
+      <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J597" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I597" s="6" t="inlineStr"/>
+      <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26326,21 +26326,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0595</v>
+        <v>-0.0174</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>14880000</v>
+        <v>4590000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>61.35</v>
+        <v>54.07</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26348,12 +26348,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26361,21 +26361,23 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>39.64</v>
+        <v>251</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.0346</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>12770000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>52.02</v>
+        <v>46.72</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26383,47 +26385,51 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L599" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr"/>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>24.62</v>
+        <v>17.32</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E600" s="2" t="inlineStr"/>
+        <v>12210000</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F600" s="3" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="G600" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G600" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="2" t="inlineStr"/>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="I600" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J600" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26431,108 +26437,92 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>13.89</v>
+        <v>103.5</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>35540000</v>
+        <v>398550</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="7" t="n">
-        <v>54.23</v>
-      </c>
+      <c r="F601" s="6" t="inlineStr"/>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr"/>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>18.99</v>
+        <v>81.84</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0495</v>
+        <v>0.0027</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>102290000</v>
+        <v>11800000</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
-      <c r="F602" s="2" t="inlineStr"/>
+      <c r="F602" s="3" t="n">
+        <v>45.85</v>
+      </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
-      <c r="K602" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="K602" s="2" t="inlineStr"/>
+      <c r="L602" s="2" t="inlineStr"/>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>2.74</v>
+        <v>4.73</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.0216</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>98340000</v>
+        <v>62450000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.7119</v>
+        <v>0.8667</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>43.27</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26540,20 +26530,22 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>103.5</v>
+        <v>16.08</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.001</v>
+        <v>-0.0111</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>398550</v>
+        <v>72700000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
-      <c r="F604" s="2" t="inlineStr"/>
+      <c r="F604" s="3" t="n">
+        <v>51.02</v>
+      </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
       <c r="I604" s="2" t="inlineStr"/>
@@ -26563,40 +26555,48 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>16.08</v>
+        <v>10.56</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0111</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>72700000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>51.02</v>
+        <v>53.86</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="6" t="inlineStr"/>
+      <c r="I605" s="8" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26604,21 +26604,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>6.13</v>
+        <v>41.38</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0016</v>
+        <v>0.0222</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>8730000</v>
+        <v>10990000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>61.01</v>
+        <v>60.95</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26626,51 +26626,51 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr"/>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+        </is>
+      </c>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>152.1</v>
+        <v>80.95</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.0247</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>2330000</v>
+        <v>32400</v>
       </c>
       <c r="E607" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.58</v>
       </c>
       <c r="F607" s="7" t="n">
-        <v>52.17</v>
+        <v>41.16</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="8" t="n">
-        <v>-3.6635</v>
+        <v>-9.409700000000001</v>
       </c>
       <c r="J607" s="8" t="n">
-        <v>-0.4897</v>
+        <v>-4.155</v>
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 10:30</t>
+          <t>23.04.2026 11:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,32 +25781,40 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>18.99</v>
+        <v>2.74</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.0495</v>
+        <v>-0.0108</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>102290000</v>
-      </c>
-      <c r="E583" s="6" t="inlineStr"/>
-      <c r="F583" s="6" t="inlineStr"/>
+        <v>98340000</v>
+      </c>
+      <c r="E583" s="8" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="F583" s="7" t="n">
+        <v>43.27</v>
+      </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
+      <c r="I583" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J583" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25814,21 +25822,21 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>169</v>
+        <v>197.4</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0236</v>
+        <v>-0.099</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>12070000</v>
+        <v>20610000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>60.59</v>
+        <v>45.87</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25836,12 +25844,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25849,21 +25857,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>6.13</v>
+        <v>16.08</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0111</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>8730000</v>
+        <v>72700000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>61.01</v>
+        <v>51.02</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25874,105 +25882,111 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L585" s="6" t="inlineStr"/>
+      <c r="L585" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>2.74</v>
+        <v>7.59</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0108</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>98340000</v>
+        <v>477650</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>0.7119</v>
+        <v>0.95</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>43.27</v>
+        <v>39.58</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="4" t="n">
-        <v>-191.6342</v>
+        <v>-23.6291</v>
       </c>
       <c r="J586" s="4" t="n">
-        <v>-0.8093</v>
+        <v>-0.4678</v>
       </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>7.59</v>
+        <v>152.1</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0225</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>477650</v>
+        <v>2330000</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.95</v>
+        <v>0.1071</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>39.58</v>
+        <v>52.17</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="8" t="n">
-        <v>-23.6291</v>
+        <v>-3.6635</v>
       </c>
       <c r="J587" s="8" t="n">
-        <v>-0.4678</v>
+        <v>-0.4897</v>
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr"/>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>251</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0595</v>
+        <v>-0.0346</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>14880000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>61.35</v>
+        <v>46.72</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25980,53 +25994,43 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>6.95</v>
+        <v>13.89</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>78.58</v>
+        <v>54.23</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J589" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26034,38 +26038,40 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>62.95</v>
+        <v>6.95</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0008</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>539710</v>
+        <v>75580000</v>
       </c>
       <c r="E590" s="4" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.1672</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>56.09</v>
+        <v>78.58</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
       <c r="J590" s="4" t="n">
-        <v>0.4139</v>
+        <v>-4.2562</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26073,21 +26079,23 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>13.89</v>
+        <v>28.66</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.0478</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>35540000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>54.23</v>
+        <v>50.42</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
@@ -26095,12 +26103,12 @@
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26108,36 +26116,42 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>28.66</v>
+        <v>17.32</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.0478</v>
+        <v>0.0058</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>18930000</v>
+        <v>12210000</v>
       </c>
       <c r="E592" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.9246</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G592" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G592" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="2" t="inlineStr"/>
-      <c r="J592" s="2" t="inlineStr"/>
+      <c r="I592" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J592" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26145,21 +26159,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>39.64</v>
+        <v>33.9</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.0174</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>12770000</v>
+        <v>4590000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>52.02</v>
+        <v>54.07</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26167,12 +26181,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26180,34 +26194,38 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>24.62</v>
+        <v>62.95</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0008</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E594" s="2" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F594" s="3" t="n">
-        <v>56.05</v>
+        <v>56.09</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="J594" s="4" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26215,22 +26233,20 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>2.82</v>
+        <v>18.99</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0537</v>
+        <v>-0.0495</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>263430000</v>
+        <v>102290000</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
-      <c r="F595" s="7" t="n">
-        <v>52.07</v>
-      </c>
+      <c r="F595" s="6" t="inlineStr"/>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
@@ -26242,7 +26258,7 @@
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26250,62 +26266,48 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>152.1</v>
+        <v>81.84</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0225</v>
+        <v>0.0027</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>11800000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>52.17</v>
+        <v>45.85</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J596" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
-      <c r="K596" s="2" t="inlineStr">
-        <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+      <c r="I596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>197.4</v>
+        <v>41.38</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.099</v>
+        <v>0.0222</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>20610000</v>
+        <v>10990000</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>45.87</v>
+        <v>60.95</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
@@ -26313,12 +26315,12 @@
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26326,21 +26328,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>33.9</v>
+        <v>2.82</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0537</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>4590000</v>
+        <v>263430000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>54.07</v>
+        <v>52.07</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26348,12 +26350,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26361,23 +26363,21 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>251</v>
+        <v>39.64</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0346</v>
+        <v>0.0195</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>12770000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>46.72</v>
+        <v>52.02</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26385,51 +26385,47 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L599" s="6" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>17.32</v>
+        <v>24.62</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>15600000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G600" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>56.05</v>
+      </c>
+      <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26437,79 +26433,93 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>103.5</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.001</v>
+        <v>-0.0595</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>398550</v>
+        <v>14880000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="6" t="inlineStr"/>
+      <c r="F601" s="7" t="n">
+        <v>61.35</v>
+      </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>81.84</v>
+        <v>4.73</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.0216</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
+        <v>62450000</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F602" s="3" t="n">
-        <v>45.85</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
-      <c r="K602" s="2" t="inlineStr"/>
-      <c r="L602" s="2" t="inlineStr"/>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>4.73</v>
+        <v>6.13</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0216</v>
+        <v>0.0016</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>77.90000000000001</v>
+        <v>61.01</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26520,44 +26530,44 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L603" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+      <c r="L603" s="6" t="inlineStr"/>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>16.08</v>
+        <v>10.56</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0111</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>72700000</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>51.02</v>
+        <v>53.86</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="2" t="inlineStr"/>
+      <c r="I604" s="4" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26565,60 +26575,58 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>10.56</v>
+        <v>80.95</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>255670000</v>
+        <v>32400</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.2479</v>
+        <v>0.58</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>53.86</v>
+        <v>41.16</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="J605" s="6" t="inlineStr"/>
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J605" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L605" s="6" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L605" s="6" t="inlineStr"/>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>41.38</v>
+        <v>169</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0236</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>10990000</v>
+        <v>12070000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>60.95</v>
+        <v>60.59</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26626,12 +26634,12 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26639,35 +26647,27 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>80.95</v>
+        <v>103.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0247</v>
+        <v>-0.001</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>32400</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F607" s="7" t="n">
-        <v>41.16</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
+      <c r="F607" s="6" t="inlineStr"/>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 11:30</t>
+          <t>23.04.2026 12:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,40 +25781,34 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>2.74</v>
+        <v>39.64</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.0195</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E583" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>12770000</v>
+      </c>
+      <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>43.27</v>
+        <v>52.02</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J583" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25822,21 +25816,21 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>197.4</v>
+        <v>33.9</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0174</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>20610000</v>
+        <v>4590000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>45.87</v>
+        <v>54.07</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25844,12 +25838,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25857,21 +25851,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>16.08</v>
+        <v>197.4</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0111</v>
+        <v>-0.099</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>72700000</v>
+        <v>20610000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>51.02</v>
+        <v>45.87</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25879,12 +25873,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25892,77 +25886,77 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>7.59</v>
+        <v>17.32</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.0058</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>477650</v>
+        <v>12210000</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>0.95</v>
+        <v>0.9246</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>39.58</v>
-      </c>
-      <c r="G586" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G586" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="4" t="n">
-        <v>-23.6291</v>
+        <v>0.0028</v>
       </c>
       <c r="J586" s="4" t="n">
-        <v>-0.4678</v>
+        <v>-10.3171</v>
       </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>152.1</v>
+        <v>13.89</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.0102</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>52.17</v>
+        <v>54.23</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25970,23 +25964,21 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>251</v>
+        <v>6.13</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0346</v>
+        <v>0.0016</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>46.72</v>
+        <v>61.01</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25994,7 +25986,7 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr"/>
@@ -26003,34 +25995,38 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>13.89</v>
+        <v>62.95</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.0008</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>35540000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F589" s="7" t="n">
-        <v>54.23</v>
+        <v>56.09</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
+      <c r="J589" s="8" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26038,64 +26034,48 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>6.95</v>
+        <v>81.84</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0027</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>11800000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>78.58</v>
+        <v>45.85</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
-      <c r="K590" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>28.66</v>
+        <v>16.08</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0478</v>
+        <v>-0.0111</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>18930000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>72700000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>50.42</v>
+        <v>51.02</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
@@ -26103,12 +26083,12 @@
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26116,77 +26096,65 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>17.32</v>
+        <v>251</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0346</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>12210000</v>
+        <v>8590</v>
       </c>
       <c r="E592" s="4" t="n">
-        <v>0.9246</v>
+        <v>0.2578</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G592" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>46.72</v>
+      </c>
+      <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr"/>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>33.9</v>
+        <v>18.99</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0174</v>
+        <v>-0.0495</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>4590000</v>
+        <v>102290000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
-      <c r="F593" s="7" t="n">
-        <v>54.07</v>
-      </c>
+      <c r="F593" s="6" t="inlineStr"/>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
       <c r="I593" s="6" t="inlineStr"/>
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26194,38 +26162,34 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>62.95</v>
+        <v>2.82</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0008</v>
+        <v>-0.0537</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>539710</v>
-      </c>
-      <c r="E594" s="4" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>263430000</v>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>56.09</v>
+        <v>52.07</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="4" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26233,17 +26197,17 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>18.99</v>
+        <v>103.5</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0495</v>
+        <v>-0.001</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>102290000</v>
+        <v>398550</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="6" t="inlineStr"/>
@@ -26256,38 +26220,44 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>81.84</v>
+        <v>28.66</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0478</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>45.85</v>
+        <v>50.42</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
       <c r="J596" s="2" t="inlineStr"/>
-      <c r="K596" s="2" t="inlineStr"/>
-      <c r="L596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
@@ -26328,34 +26298,40 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.0108</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>98340000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>52.07</v>
+        <v>43.27</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="I598" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26363,34 +26339,38 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>39.64</v>
+        <v>10.56</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>12770000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>52.02</v>
+        <v>53.86</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26398,36 +26378,38 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>24.62</v>
+        <v>80.95</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E600" s="2" t="inlineStr"/>
+        <v>32400</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F600" s="3" t="n">
-        <v>56.05</v>
+        <v>41.16</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="2" t="inlineStr"/>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="I600" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J600" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
@@ -26468,23 +26450,21 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>4.73</v>
+        <v>24.62</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>15600000</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>56.05</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
@@ -26492,12 +26472,12 @@
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26505,69 +26485,75 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>6.13</v>
+        <v>6.95</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>8730000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>61.01</v>
+        <v>78.58</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
         </is>
       </c>
-      <c r="L603" s="6" t="inlineStr"/>
+      <c r="L603" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>10.56</v>
+        <v>169</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.0236</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>255670000</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.2479</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>53.86</v>
+        <v>60.59</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="4" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
+      <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26575,35 +26561,35 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>80.95</v>
+        <v>7.59</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0247</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>32400</v>
+        <v>477650</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.58</v>
+        <v>0.95</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>41.16</v>
+        <v>39.58</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="8" t="n">
-        <v>-9.409700000000001</v>
+        <v>-23.6291</v>
       </c>
       <c r="J605" s="8" t="n">
-        <v>-4.155</v>
+        <v>-0.4678</v>
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -26612,34 +26598,40 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>169</v>
+        <v>152.1</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0236</v>
+        <v>-0.0225</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>60.59</v>
+        <v>52.17</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26647,20 +26639,24 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>103.5</v>
+        <v>4.73</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.0216</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>398550</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
-      <c r="F607" s="6" t="inlineStr"/>
+        <v>62450000</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="F607" s="7" t="n">
+        <v>77.90000000000001</v>
+      </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="6" t="inlineStr"/>
@@ -26670,7 +26666,11 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L607" s="6" t="inlineStr"/>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 12:30</t>
+          <t>23.04.2026 13:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25781,21 +25781,21 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>39.64</v>
+        <v>6.13</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0016</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>12770000</v>
+        <v>8730000</v>
       </c>
       <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>52.02</v>
+        <v>61.01</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
@@ -25803,34 +25803,30 @@
       <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr"/>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>33.9</v>
+        <v>2.82</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0537</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>4590000</v>
+        <v>263430000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>54.07</v>
+        <v>52.07</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25838,12 +25834,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25851,34 +25847,38 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>197.4</v>
+        <v>10.56</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.099</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>20610000</v>
-      </c>
-      <c r="E585" s="6" t="inlineStr"/>
+        <v>255670000</v>
+      </c>
+      <c r="E585" s="8" t="n">
+        <v>0.2479</v>
+      </c>
       <c r="F585" s="7" t="n">
-        <v>45.87</v>
+        <v>53.86</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="6" t="inlineStr"/>
+      <c r="I585" s="8" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25886,64 +25886,54 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>17.32</v>
+        <v>251</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0346</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>12210000</v>
+        <v>8590</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>0.9246</v>
+        <v>0.2578</v>
       </c>
       <c r="F586" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G586" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>46.72</v>
+      </c>
+      <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J586" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>13.89</v>
+        <v>41.38</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.0222</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>35540000</v>
+        <v>10990000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>54.23</v>
+        <v>60.95</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25951,12 +25941,12 @@
       <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25964,29 +25954,35 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>6.13</v>
+        <v>80.95</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0016</v>
+        <v>0.0247</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>8730000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>32400</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>61.01</v>
+        <v>41.16</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="2" t="inlineStr"/>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="I588" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J588" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr"/>
@@ -25995,38 +25991,36 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>62.95</v>
+        <v>4.73</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0008</v>
+        <v>0.0216</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>539710</v>
+        <v>62450000</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.8667</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>56.09</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26034,61 +26028,75 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>81.84</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0595</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>11800000</v>
+        <v>14880000</v>
       </c>
       <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>45.85</v>
+        <v>61.35</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
       <c r="I590" s="2" t="inlineStr"/>
       <c r="J590" s="2" t="inlineStr"/>
-      <c r="K590" s="2" t="inlineStr"/>
-      <c r="L590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>16.08</v>
+        <v>152.1</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0111</v>
+        <v>-0.0225</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>72700000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>51.02</v>
+        <v>52.17</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26096,23 +26104,21 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>251</v>
+        <v>16.08</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0111</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>72700000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>46.72</v>
+        <v>51.02</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26120,41 +26126,47 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>18.99</v>
+        <v>197.4</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0495</v>
+        <v>-0.099</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>102290000</v>
+        <v>20610000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
-      <c r="F593" s="6" t="inlineStr"/>
+      <c r="F593" s="7" t="n">
+        <v>45.87</v>
+      </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
       <c r="I593" s="6" t="inlineStr"/>
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26162,26 +26174,32 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>2.82</v>
+        <v>6.95</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E594" s="2" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F594" s="3" t="n">
-        <v>52.07</v>
+        <v>78.58</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="I594" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J594" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26189,7 +26207,7 @@
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26197,141 +26215,141 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>103.5</v>
+        <v>28.66</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.001</v>
+        <v>-0.0478</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>398550</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
-      <c r="F595" s="6" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="F595" s="7" t="n">
+        <v>50.42</v>
+      </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>28.66</v>
+        <v>7.59</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0478</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>18930000</v>
+        <v>477650</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.95</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>50.42</v>
+        <v>39.58</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J596" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>41.38</v>
+        <v>103.5</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0222</v>
+        <v>-0.001</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>10990000</v>
+        <v>398550</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
-      <c r="F597" s="7" t="n">
-        <v>60.95</v>
-      </c>
+      <c r="F597" s="6" t="inlineStr"/>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="6" t="inlineStr"/>
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L597" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L597" s="6" t="inlineStr"/>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>2.74</v>
+        <v>62.95</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0108</v>
+        <v>-0.0008</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>98340000</v>
+        <v>539710</v>
       </c>
       <c r="E598" s="4" t="n">
-        <v>0.7119</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F598" s="3" t="n">
-        <v>43.27</v>
+        <v>56.09</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
+      <c r="I598" s="2" t="inlineStr"/>
       <c r="J598" s="4" t="n">
-        <v>-0.8093</v>
+        <v>0.4139</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26339,38 +26357,40 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>10.56</v>
+        <v>2.74</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.08529999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>255670000</v>
+        <v>98340000</v>
       </c>
       <c r="E599" s="8" t="n">
-        <v>0.2479</v>
+        <v>0.7119</v>
       </c>
       <c r="F599" s="7" t="n">
-        <v>53.86</v>
+        <v>43.27</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="J599" s="6" t="inlineStr"/>
+        <v>-191.6342</v>
+      </c>
+      <c r="J599" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26378,58 +26398,56 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>80.95</v>
+        <v>169</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0247</v>
+        <v>0.0236</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>32400</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>12070000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>41.16</v>
+        <v>60.59</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>90.84999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0595</v>
+        <v>-0.0174</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>14880000</v>
+        <v>4590000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>61.35</v>
+        <v>54.07</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
@@ -26437,12 +26455,12 @@
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26450,34 +26468,32 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>24.62</v>
+        <v>18.99</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0495</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>15600000</v>
+        <v>102290000</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
-      <c r="F602" s="3" t="n">
-        <v>56.05</v>
-      </c>
+      <c r="F602" s="2" t="inlineStr"/>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26485,40 +26501,34 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>6.95</v>
+        <v>39.64</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>12770000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>78.58</v>
+        <v>52.02</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26526,112 +26536,96 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>169</v>
+        <v>81.84</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0236</v>
+        <v>0.0027</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>12070000</v>
+        <v>11800000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>60.59</v>
+        <v>45.85</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
       <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr"/>
-      <c r="K604" s="2" t="inlineStr">
-        <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>7.59</v>
+        <v>24.62</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E605" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>15600000</v>
+      </c>
+      <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>39.58</v>
+        <v>56.05</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J605" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L605" s="6" t="inlineStr"/>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L605" s="6" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>152.1</v>
+        <v>13.89</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0225</v>
+        <v>0.0102</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>52.17</v>
+        <v>54.23</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J606" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26639,36 +26633,42 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>4.73</v>
+        <v>17.32</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0216</v>
+        <v>0.0058</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>62450000</v>
+        <v>12210000</v>
       </c>
       <c r="E607" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.9246</v>
       </c>
       <c r="F607" s="7" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="G607" s="6" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G607" s="7" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 13:30</t>
+          <t>23.04.2026 14:38</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -7359,44 +7359,42 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>KIMMR</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B159" s="7" t="n">
-        <v>17.58</v>
+        <v>115.2</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>0.005699999999999999</v>
+        <v>-0.012</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>2240000</v>
+        <v>2650000</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>0.2708</v>
+        <v>0.1496</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="G159" s="7" t="n">
-        <v>6.66</v>
-      </c>
+        <v>50.92</v>
+      </c>
+      <c r="G159" s="6" t="inlineStr"/>
       <c r="H159" s="7" t="n">
         <v>0.96</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>0.1738</v>
+        <v>-0.1125</v>
       </c>
       <c r="J159" s="8" t="n">
-        <v>2.5571</v>
+        <v>0.0537</v>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
@@ -7404,44 +7402,44 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>KIMMR</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>114.1</v>
+        <v>17.58</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>-0.0104</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>18880000</v>
+        <v>2240000</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>0.4894</v>
+        <v>0.2708</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>52.11</v>
+        <v>49.32</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>14.75</v>
+        <v>6.66</v>
       </c>
       <c r="H160" s="3" t="n">
         <v>0.96</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0.07629999999999999</v>
+        <v>0.1738</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>-0.2259</v>
+        <v>2.5571</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -7449,126 +7447,126 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>KERVN</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B161" s="7" t="n">
-        <v>4.01</v>
+        <v>114.1</v>
       </c>
       <c r="C161" s="8" t="n">
-        <v>0.0665</v>
+        <v>-0.0104</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1070000</v>
+        <v>18880000</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>0.3049</v>
+        <v>0.4894</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
+        <v>52.11</v>
+      </c>
+      <c r="G161" s="7" t="n">
+        <v>14.75</v>
+      </c>
       <c r="H161" s="7" t="n">
         <v>0.96</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.0213</v>
-      </c>
-      <c r="J161" s="6" t="inlineStr"/>
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="J161" s="8" t="n">
+        <v>-0.2259</v>
+      </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
-        </is>
-      </c>
-      <c r="L161" s="6" t="inlineStr"/>
+          <t>İletişim</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+        </is>
+      </c>
       <c r="M161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>YUNSA</t>
+          <t>KERVN</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>4.01</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>-0.0112</v>
+        <v>0.0665</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>6880000</v>
+        <v>1070000</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>0.4212</v>
+        <v>0.3049</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>56.66</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>11.58</v>
-      </c>
+        <v>51.9</v>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="3" t="n">
         <v>0.96</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="J162" s="4" t="n">
-        <v>-0.5928</v>
-      </c>
+        <v>-0.0213</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
       <c r="M162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>YUNSA</t>
         </is>
       </c>
       <c r="B163" s="7" t="n">
-        <v>85.95</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>-0.025</v>
+        <v>-0.0112</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>9340000</v>
+        <v>6880000</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>0.1877</v>
+        <v>0.4212</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>27.05</v>
+        <v>56.66</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>31.81</v>
+        <v>11.58</v>
       </c>
       <c r="H163" s="7" t="n">
         <v>0.96</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0941</v>
       </c>
       <c r="J163" s="8" t="n">
-        <v>-1.9718</v>
+        <v>-0.5928</v>
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr"/>
@@ -7576,40 +7574,44 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>BORSK</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>7.16</v>
+        <v>85.95</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>-0.0363</v>
+        <v>-0.025</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>13990000</v>
+        <v>9340000</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>0.6457999999999999</v>
+        <v>0.1877</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
+        <v>27.05</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>31.81</v>
+      </c>
       <c r="H164" s="3" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr"/>
+        <v>0.035</v>
+      </c>
+      <c r="J164" s="4" t="n">
+        <v>-1.9718</v>
+      </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr"/>
@@ -7617,42 +7619,40 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>GSRAY</t>
+          <t>BORSK</t>
         </is>
       </c>
       <c r="B165" s="7" t="n">
-        <v>1.16</v>
+        <v>7.16</v>
       </c>
       <c r="C165" s="8" t="n">
-        <v>0</v>
+        <v>-0.0363</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>288640000</v>
+        <v>13990000</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>0.3999</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>58.04</v>
+        <v>58.06</v>
       </c>
       <c r="G165" s="6" t="inlineStr"/>
       <c r="H165" s="7" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.0873</v>
-      </c>
-      <c r="J165" s="8" t="n">
-        <v>-1.5758</v>
-      </c>
+        <v>-0.0042</v>
+      </c>
+      <c r="J165" s="6" t="inlineStr"/>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr"/>
@@ -7660,42 +7660,42 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>GSRAY</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>73.34999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>0.04190000000000001</v>
+        <v>0</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>8600000</v>
+        <v>288640000</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>0.653</v>
+        <v>0.3999</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>67.95</v>
+        <v>58.04</v>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-0.0231</v>
+        <v>-0.0873</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>-0.0625</v>
+        <v>-1.5758</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr"/>
@@ -7703,42 +7703,42 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>REEDR</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="B167" s="7" t="n">
-        <v>8.050000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="C167" s="8" t="n">
-        <v>-0.0405</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="D167" s="9" t="n">
-        <v>90010000</v>
+        <v>8600000</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>0.3803</v>
+        <v>0.653</v>
       </c>
       <c r="F167" s="7" t="n">
-        <v>56.61</v>
+        <v>67.95</v>
       </c>
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="7" t="n">
         <v>0.99</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.1566</v>
+        <v>-0.0231</v>
       </c>
       <c r="J167" s="8" t="n">
-        <v>0.7471</v>
+        <v>-0.0625</v>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr"/>
@@ -7746,44 +7746,42 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GWIND</t>
+          <t>REEDR</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>25.94</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>-0.0077</v>
+        <v>-0.0405</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>7420000</v>
+        <v>90010000</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>0.3</v>
+        <v>0.3803</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>17.37</v>
-      </c>
+        <v>56.61</v>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="3" t="n">
         <v>0.99</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>-0.1566</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>-0.6212</v>
+        <v>0.7471</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BALIKESİR</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr"/>
@@ -7791,42 +7789,44 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>GWIND</t>
         </is>
       </c>
       <c r="B169" s="7" t="n">
-        <v>115.2</v>
+        <v>25.94</v>
       </c>
       <c r="C169" s="8" t="n">
-        <v>-0.012</v>
+        <v>-0.0077</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>2650000</v>
+        <v>7420000</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>0.1496</v>
+        <v>0.3</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="G169" s="6" t="inlineStr"/>
+        <v>40.78</v>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>17.37</v>
+      </c>
       <c r="H169" s="7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1156</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="J169" s="8" t="n">
-        <v>0.0659</v>
+        <v>-0.6212</v>
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr"/>
@@ -8323,44 +8323,42 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ATAKP</t>
         </is>
       </c>
       <c r="B181" s="7" t="n">
-        <v>14.39</v>
+        <v>52</v>
       </c>
       <c r="C181" s="8" t="n">
-        <v>-0.0157</v>
+        <v>-0.0441</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>12600000</v>
+        <v>769720</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>0.7115</v>
+        <v>0.2034</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>45.06</v>
-      </c>
-      <c r="G181" s="7" t="n">
-        <v>2.61</v>
-      </c>
+        <v>44.04</v>
+      </c>
+      <c r="G181" s="6" t="inlineStr"/>
       <c r="H181" s="7" t="n">
         <v>1.06</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>0.5625</v>
+        <v>-0.0317</v>
       </c>
       <c r="J181" s="8" t="n">
-        <v>4.1559</v>
+        <v>0.1112</v>
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M181" s="6" t="inlineStr"/>
@@ -8368,35 +8366,35 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>273.5</v>
+        <v>14.39</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.0018</v>
+        <v>-0.0157</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>172890</v>
+        <v>12600000</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>0.3301</v>
+        <v>0.7115</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>48.19</v>
+        <v>45.06</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>15.79</v>
+        <v>2.61</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>1.06</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.07629999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>2.0964</v>
+        <v>4.1559</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -8405,7 +8403,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST TEMETTU, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr"/>
@@ -8413,42 +8411,44 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B183" s="7" t="n">
-        <v>3.86</v>
+        <v>273.5</v>
       </c>
       <c r="C183" s="8" t="n">
-        <v>-0.0277</v>
+        <v>0.0018</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>230000000</v>
+        <v>172890</v>
       </c>
       <c r="E183" s="8" t="n">
-        <v>0.3512</v>
+        <v>0.3301</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>63.74</v>
-      </c>
-      <c r="G183" s="6" t="inlineStr"/>
+        <v>48.19</v>
+      </c>
+      <c r="G183" s="7" t="n">
+        <v>15.79</v>
+      </c>
       <c r="H183" s="7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.131</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="J183" s="8" t="n">
-        <v>-4.6418</v>
+        <v>2.0964</v>
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST TEMETTU, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr"/>
@@ -8456,44 +8456,42 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>6.8</v>
+        <v>3.86</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>-0.0058</v>
+        <v>-0.0277</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>5380000</v>
+        <v>230000000</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>0.501</v>
+        <v>0.3512</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>7.22</v>
-      </c>
+        <v>63.74</v>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="3" t="n">
         <v>1.07</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.1769</v>
+        <v>-0.131</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>1.394</v>
+        <v>-4.6418</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr"/>
@@ -8501,33 +8499,35 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>KTSKR</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B185" s="7" t="n">
-        <v>134.6</v>
+        <v>6.8</v>
       </c>
       <c r="C185" s="8" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="D185" s="7" t="n">
-        <v>4140000</v>
+        <v>-0.0058</v>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>5380000</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>0.3086</v>
+        <v>0.501</v>
       </c>
       <c r="F185" s="7" t="n">
-        <v>74.37</v>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
+        <v>64.18000000000001</v>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>7.22</v>
+      </c>
       <c r="H185" s="7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.019</v>
+        <v>0.1769</v>
       </c>
       <c r="J185" s="8" t="n">
-        <v>-4.305400000000001</v>
+        <v>1.394</v>
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="L185" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr"/>
@@ -8544,42 +8544,42 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>AGROT</t>
+          <t>KTSKR</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>3.35</v>
+        <v>134.6</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>-0.0205</v>
-      </c>
-      <c r="D186" s="5" t="n">
-        <v>248580000</v>
+        <v>-0.0239</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>4140000</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>0.3517</v>
+        <v>0.3086</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>57.73</v>
+        <v>74.37</v>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>-0.0902</v>
+        <v>-0.019</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>-0.5942000000000001</v>
+        <v>-4.305400000000001</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr"/>
@@ -8587,42 +8587,42 @@
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>AGROT</t>
         </is>
       </c>
       <c r="B187" s="7" t="n">
-        <v>84.65000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="C187" s="8" t="n">
-        <v>-0.0276</v>
+        <v>-0.0205</v>
       </c>
       <c r="D187" s="9" t="n">
-        <v>205860</v>
+        <v>248580000</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>0.1275</v>
+        <v>0.3517</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>47.82</v>
+        <v>57.73</v>
       </c>
       <c r="G187" s="6" t="inlineStr"/>
       <c r="H187" s="7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>-0.0451</v>
+        <v>-0.0902</v>
       </c>
       <c r="J187" s="8" t="n">
-        <v>-1.622</v>
+        <v>-0.5942000000000001</v>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM TEMETTU, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
@@ -8630,42 +8630,42 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>EGSER</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>3.04</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>0.027</v>
+        <v>-0.0276</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>3650000</v>
+        <v>205860</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>0.3306</v>
+        <v>0.1275</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>64.17</v>
+        <v>47.82</v>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>-0.4584</v>
+        <v>-0.0451</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>-0.3601</v>
+        <v>-1.622</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM TEMETTU, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr"/>
@@ -8673,44 +8673,42 @@
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>EGSER</t>
         </is>
       </c>
       <c r="B189" s="7" t="n">
-        <v>9.83</v>
+        <v>3.04</v>
       </c>
       <c r="C189" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.027</v>
       </c>
       <c r="D189" s="9" t="n">
-        <v>10460000</v>
+        <v>3650000</v>
       </c>
       <c r="E189" s="8" t="n">
-        <v>0.599</v>
+        <v>0.3306</v>
       </c>
       <c r="F189" s="7" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="G189" s="7" t="n">
-        <v>14.8</v>
-      </c>
+        <v>64.17</v>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
       <c r="H189" s="7" t="n">
         <v>1.1</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.4584</v>
       </c>
       <c r="J189" s="8" t="n">
-        <v>0.6942</v>
+        <v>-0.3601</v>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr"/>
@@ -8718,44 +8716,44 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AKYHO</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>2.73</v>
+        <v>9.83</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.001</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>3030000</v>
+        <v>10460000</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>0.9801000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>6825</v>
+        <v>62.35</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0.0002</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>-2.3862</v>
+        <v>0.6942</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr"/>
@@ -8763,42 +8761,44 @@
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>EYGYO</t>
+          <t>AKYHO</t>
         </is>
       </c>
       <c r="B191" s="7" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0073</v>
       </c>
       <c r="D191" s="9" t="n">
-        <v>21560000</v>
+        <v>3030000</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>0.314</v>
+        <v>0.9801000000000001</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>47.57</v>
-      </c>
-      <c r="G191" s="6" t="inlineStr"/>
+        <v>55.7</v>
+      </c>
+      <c r="G191" s="9" t="n">
+        <v>6825</v>
+      </c>
       <c r="H191" s="7" t="n">
         <v>1.11</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>-0.3417</v>
+        <v>0.0002</v>
       </c>
       <c r="J191" s="8" t="n">
-        <v>-2.1476</v>
+        <v>-2.3862</v>
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr"/>
@@ -8806,35 +8806,33 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>EYGYO</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>3.71</v>
+        <v>2.9</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0102</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>127370000</v>
+        <v>21560000</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>0.7881999999999999</v>
+        <v>0.314</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="G192" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>47.57</v>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>0.1155</v>
+        <v>-0.3417</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>0.1014</v>
+        <v>-2.1476</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -8843,7 +8841,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr"/>
@@ -8851,42 +8849,44 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>SAMAT</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="B193" s="7" t="n">
-        <v>5.6</v>
+        <v>3.71</v>
       </c>
       <c r="C193" s="8" t="n">
-        <v>-0.0295</v>
+        <v>0.0027</v>
       </c>
       <c r="D193" s="9" t="n">
-        <v>2040000</v>
+        <v>127370000</v>
       </c>
       <c r="E193" s="8" t="n">
-        <v>0.2951</v>
+        <v>0.7881999999999999</v>
       </c>
       <c r="F193" s="7" t="n">
-        <v>54.96</v>
+        <v>62.28</v>
       </c>
       <c r="G193" s="7" t="n">
-        <v>34.74</v>
+        <v>24</v>
       </c>
       <c r="H193" s="7" t="n">
         <v>1.12</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="J193" s="6" t="inlineStr"/>
+        <v>0.1155</v>
+      </c>
+      <c r="J193" s="8" t="n">
+        <v>0.1014</v>
+      </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M193" s="6" t="inlineStr"/>
@@ -8894,42 +8894,42 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CEMAS</t>
+          <t>SAMAT</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0295</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>29020000</v>
+        <v>2040000</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.2951</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>50.26</v>
-      </c>
-      <c r="G194" s="2" t="inlineStr"/>
+        <v>54.96</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>34.74</v>
+      </c>
       <c r="H194" s="3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>-0.3776</v>
-      </c>
-      <c r="J194" s="4" t="n">
-        <v>-5.3326</v>
-      </c>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr"/>
@@ -8937,42 +8937,42 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>SELVA</t>
+          <t>CEMAS</t>
         </is>
       </c>
       <c r="B195" s="7" t="n">
-        <v>2.69</v>
+        <v>5</v>
       </c>
       <c r="C195" s="8" t="n">
-        <v>0.098</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="D195" s="9" t="n">
-        <v>109770000</v>
+        <v>29020000</v>
       </c>
       <c r="E195" s="8" t="n">
-        <v>0.6808</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="F195" s="7" t="n">
-        <v>66.92</v>
+        <v>50.26</v>
       </c>
       <c r="G195" s="6" t="inlineStr"/>
       <c r="H195" s="7" t="n">
         <v>1.13</v>
       </c>
       <c r="I195" s="8" t="n">
-        <v>-0.2143</v>
+        <v>-0.3776</v>
       </c>
       <c r="J195" s="8" t="n">
-        <v>-4.419</v>
+        <v>-5.3326</v>
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
@@ -8980,42 +8980,42 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>SELVA</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>43.58</v>
+        <v>2.69</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>-0.0009</v>
+        <v>0.098</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>888590</v>
+        <v>109770000</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>0.2133</v>
+        <v>0.6808</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>51.65</v>
+        <v>66.92</v>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="3" t="n">
         <v>1.13</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-0.0635</v>
+        <v>-0.2143</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>-0.0447</v>
+        <v>-4.419</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST KONYA</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr"/>
@@ -9023,42 +9023,42 @@
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>BOBET</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B197" s="7" t="n">
-        <v>20.08</v>
+        <v>43.58</v>
       </c>
       <c r="C197" s="8" t="n">
-        <v>0.003</v>
+        <v>-0.0009</v>
       </c>
       <c r="D197" s="9" t="n">
-        <v>4520000</v>
+        <v>888590</v>
       </c>
       <c r="E197" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2133</v>
       </c>
       <c r="F197" s="7" t="n">
-        <v>54.61</v>
+        <v>51.65</v>
       </c>
       <c r="G197" s="6" t="inlineStr"/>
       <c r="H197" s="7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.1716</v>
+        <v>-0.0635</v>
       </c>
       <c r="J197" s="8" t="n">
-        <v>-2.2777</v>
+        <v>-0.0447</v>
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
@@ -9066,44 +9066,42 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>BOBET</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>5.53</v>
+        <v>20.08</v>
       </c>
       <c r="C198" s="4" t="n">
-        <v>0.0336</v>
+        <v>0.003</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>143620000</v>
+        <v>4520000</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>0.4953</v>
+        <v>0.3</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>15.53</v>
-      </c>
+        <v>54.61</v>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="3" t="n">
         <v>1.14</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.1716</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>-2.2043</v>
+        <v>-2.2777</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr"/>
@@ -9111,126 +9109,128 @@
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>SNPAM</t>
+          <t>EUREN</t>
         </is>
       </c>
       <c r="B199" s="7" t="n">
-        <v>21.2</v>
+        <v>5.53</v>
       </c>
       <c r="C199" s="8" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="D199" s="9" t="n">
-        <v>66620</v>
+        <v>143620000</v>
       </c>
       <c r="E199" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.4953</v>
       </c>
       <c r="F199" s="7" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="G199" s="6" t="inlineStr"/>
+        <v>65.7</v>
+      </c>
+      <c r="G199" s="7" t="n">
+        <v>15.53</v>
+      </c>
       <c r="H199" s="7" t="n">
         <v>1.14</v>
       </c>
       <c r="I199" s="8" t="n">
-        <v>-0.0486</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J199" s="8" t="n">
-        <v>-2.9048</v>
+        <v>-2.2043</v>
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L199" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TLMAN</t>
+          <t>SNPAM</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>241080</v>
+        <v>66620</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>0.4279</v>
+        <v>0.0414</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G200" s="3" t="n">
-        <v>37.65</v>
-      </c>
+        <v>47.23</v>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="3" t="n">
         <v>1.14</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>0.0354</v>
+        <v>-0.0486</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>-6.6864</v>
+        <v>-2.9048</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="inlineStr">
-        <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>TLMAN</t>
         </is>
       </c>
       <c r="B201" s="7" t="n">
-        <v>201.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C201" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.0021</v>
       </c>
       <c r="D201" s="9" t="n">
-        <v>65060</v>
+        <v>241080</v>
       </c>
       <c r="E201" s="8" t="n">
-        <v>0.7088</v>
+        <v>0.4279</v>
       </c>
       <c r="F201" s="7" t="n">
-        <v>59.09</v>
-      </c>
-      <c r="G201" s="6" t="inlineStr"/>
+        <v>59.9</v>
+      </c>
+      <c r="G201" s="7" t="n">
+        <v>37.65</v>
+      </c>
       <c r="H201" s="7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I201" s="8" t="n">
-        <v>-0.0342</v>
+        <v>0.0354</v>
       </c>
       <c r="J201" s="8" t="n">
-        <v>0.1735</v>
+        <v>-6.6864</v>
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST KAYSERİ</t>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M201" s="6" t="inlineStr"/>
@@ -9238,42 +9238,42 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ATAKP</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>52</v>
+        <v>201.4</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>-0.0441</v>
+        <v>-0.001</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>769720</v>
+        <v>65060</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>0.2034</v>
+        <v>0.7088</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>44.04</v>
+        <v>59.09</v>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="3" t="n">
         <v>1.15</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-0.0149</v>
+        <v>-0.0342</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>-6.0927</v>
+        <v>0.1735</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr"/>
@@ -21473,44 +21473,42 @@
     <row r="483">
       <c r="A483" s="6" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B483" s="7" t="n">
-        <v>32</v>
+        <v>10.56</v>
       </c>
       <c r="C483" s="8" t="n">
-        <v>-0.0516</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="D483" s="9" t="n">
-        <v>30470000</v>
+        <v>255670000</v>
       </c>
       <c r="E483" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2479</v>
       </c>
       <c r="F483" s="7" t="n">
-        <v>43.13</v>
+        <v>53.86</v>
       </c>
       <c r="G483" s="7" t="n">
-        <v>123.6</v>
+        <v>7.6</v>
       </c>
       <c r="H483" s="7" t="n">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="I483" s="8" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="J483" s="8" t="n">
-        <v>-0.8634000000000001</v>
-      </c>
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="J483" s="6" t="inlineStr"/>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST BURSA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M483" s="6" t="inlineStr"/>
@@ -21518,44 +21516,44 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>MARKA</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B484" s="3" t="n">
-        <v>54.15</v>
+        <v>32</v>
       </c>
       <c r="C484" s="4" t="n">
-        <v>-0.0199</v>
+        <v>-0.0516</v>
       </c>
       <c r="D484" s="5" t="n">
-        <v>4910000</v>
+        <v>30470000</v>
       </c>
       <c r="E484" s="4" t="n">
-        <v>0.8669</v>
+        <v>0.3</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>55.74</v>
+        <v>43.13</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>10.91</v>
+        <v>123.6</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="I484" s="4" t="n">
-        <v>0.5207999999999999</v>
+        <v>0.0118</v>
       </c>
       <c r="J484" s="4" t="n">
-        <v>-0.9906</v>
+        <v>-0.8634000000000001</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L484" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST BURSA</t>
         </is>
       </c>
       <c r="M484" s="2" t="inlineStr"/>
@@ -21563,42 +21561,44 @@
     <row r="485">
       <c r="A485" s="6" t="inlineStr">
         <is>
-          <t>ANELE</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="B485" s="7" t="n">
-        <v>46.3</v>
+        <v>54.15</v>
       </c>
       <c r="C485" s="8" t="n">
-        <v>0.0998</v>
+        <v>-0.0199</v>
       </c>
       <c r="D485" s="9" t="n">
-        <v>5540000</v>
+        <v>4910000</v>
       </c>
       <c r="E485" s="8" t="n">
-        <v>0.5565</v>
+        <v>0.8669</v>
       </c>
       <c r="F485" s="7" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="G485" s="6" t="inlineStr"/>
+        <v>55.74</v>
+      </c>
+      <c r="G485" s="7" t="n">
+        <v>10.91</v>
+      </c>
       <c r="H485" s="7" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="I485" s="8" t="n">
-        <v>-0.2085</v>
+        <v>0.5207999999999999</v>
       </c>
       <c r="J485" s="8" t="n">
-        <v>-10.4842</v>
+        <v>-0.9906</v>
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M485" s="6" t="inlineStr"/>
@@ -21606,42 +21606,42 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>BAHKM</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="B486" s="3" t="n">
-        <v>113.5</v>
+        <v>46.3</v>
       </c>
       <c r="C486" s="4" t="n">
-        <v>-0.0173</v>
+        <v>0.0998</v>
       </c>
       <c r="D486" s="5" t="n">
-        <v>573270</v>
+        <v>5540000</v>
       </c>
       <c r="E486" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.5565</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>34.17</v>
+        <v>96.5</v>
       </c>
       <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="3" t="n">
-        <v>5.15</v>
+        <v>5.12</v>
       </c>
       <c r="I486" s="4" t="n">
-        <v>-0.2254</v>
+        <v>-0.2085</v>
       </c>
       <c r="J486" s="4" t="n">
-        <v>-12.5699</v>
+        <v>-10.4842</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L486" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M486" s="2" t="inlineStr"/>
@@ -21649,44 +21649,42 @@
     <row r="487">
       <c r="A487" s="6" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>BAHKM</t>
         </is>
       </c>
       <c r="B487" s="7" t="n">
-        <v>77.8</v>
+        <v>113.5</v>
       </c>
       <c r="C487" s="8" t="n">
-        <v>-0.0152</v>
+        <v>-0.0173</v>
       </c>
       <c r="D487" s="9" t="n">
-        <v>9530000</v>
+        <v>573270</v>
       </c>
       <c r="E487" s="8" t="n">
-        <v>0.4066</v>
+        <v>0.3792</v>
       </c>
       <c r="F487" s="7" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="G487" s="7" t="n">
-        <v>14.03</v>
-      </c>
+        <v>34.17</v>
+      </c>
+      <c r="G487" s="6" t="inlineStr"/>
       <c r="H487" s="7" t="n">
-        <v>5.19</v>
+        <v>5.15</v>
       </c>
       <c r="I487" s="8" t="n">
-        <v>0.3856</v>
+        <v>-0.2254</v>
       </c>
       <c r="J487" s="8" t="n">
-        <v>0.1363</v>
+        <v>-12.5699</v>
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST YILDIZ, BIST KAYSERİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M487" s="6" t="inlineStr"/>
@@ -21694,40 +21692,44 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>GEREL</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B488" s="3" t="n">
-        <v>38.8</v>
+        <v>77.8</v>
       </c>
       <c r="C488" s="4" t="n">
-        <v>0.0397</v>
+        <v>-0.0152</v>
       </c>
       <c r="D488" s="5" t="n">
-        <v>9080000</v>
+        <v>9530000</v>
       </c>
       <c r="E488" s="4" t="n">
-        <v>0.556</v>
+        <v>0.4066</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>69.02</v>
-      </c>
-      <c r="G488" s="2" t="inlineStr"/>
+        <v>52.77</v>
+      </c>
+      <c r="G488" s="3" t="n">
+        <v>14.03</v>
+      </c>
       <c r="H488" s="3" t="n">
         <v>5.19</v>
       </c>
       <c r="I488" s="4" t="n">
-        <v>-0.0561</v>
-      </c>
-      <c r="J488" s="2" t="inlineStr"/>
+        <v>0.3856</v>
+      </c>
+      <c r="J488" s="4" t="n">
+        <v>0.1363</v>
+      </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L488" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST YILDIZ, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M488" s="2" t="inlineStr"/>
@@ -21735,44 +21737,40 @@
     <row r="489">
       <c r="A489" s="6" t="inlineStr">
         <is>
-          <t>SDTTR</t>
+          <t>GEREL</t>
         </is>
       </c>
       <c r="B489" s="7" t="n">
-        <v>218.5</v>
+        <v>38.8</v>
       </c>
       <c r="C489" s="8" t="n">
-        <v>-0.05</v>
+        <v>0.0397</v>
       </c>
       <c r="D489" s="9" t="n">
-        <v>2370000</v>
+        <v>9080000</v>
       </c>
       <c r="E489" s="8" t="n">
-        <v>0.3457</v>
+        <v>0.556</v>
       </c>
       <c r="F489" s="7" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="G489" s="7" t="n">
-        <v>329.36</v>
-      </c>
+        <v>69.02</v>
+      </c>
+      <c r="G489" s="6" t="inlineStr"/>
       <c r="H489" s="7" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="I489" s="8" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="J489" s="8" t="n">
-        <v>-0.6491</v>
-      </c>
+        <v>-0.0561</v>
+      </c>
+      <c r="J489" s="6" t="inlineStr"/>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M489" s="6" t="inlineStr"/>
@@ -21780,42 +21778,44 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>SDTTR</t>
         </is>
       </c>
       <c r="B490" s="3" t="n">
-        <v>22.66</v>
+        <v>218.5</v>
       </c>
       <c r="C490" s="4" t="n">
-        <v>0.0619</v>
+        <v>-0.05</v>
       </c>
       <c r="D490" s="5" t="n">
-        <v>3110000</v>
+        <v>2370000</v>
       </c>
       <c r="E490" s="4" t="n">
-        <v>0.62</v>
+        <v>0.3457</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>66.56</v>
+        <v>48.93</v>
       </c>
       <c r="G490" s="3" t="n">
-        <v>27.11</v>
+        <v>329.36</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="I490" s="4" t="n">
-        <v>0.2536</v>
-      </c>
-      <c r="J490" s="2" t="inlineStr"/>
+        <v>0.018</v>
+      </c>
+      <c r="J490" s="4" t="n">
+        <v>-0.6491</v>
+      </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L490" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
         </is>
       </c>
       <c r="M490" s="2" t="inlineStr"/>
@@ -21823,42 +21823,42 @@
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
         <is>
-          <t>INGRM</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B491" s="7" t="n">
-        <v>427</v>
+        <v>22.66</v>
       </c>
       <c r="C491" s="8" t="n">
-        <v>0.0289</v>
+        <v>0.0619</v>
       </c>
       <c r="D491" s="9" t="n">
-        <v>51020</v>
+        <v>3110000</v>
       </c>
       <c r="E491" s="8" t="n">
-        <v>0.0842</v>
+        <v>0.62</v>
       </c>
       <c r="F491" s="7" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="G491" s="6" t="inlineStr"/>
+        <v>66.56</v>
+      </c>
+      <c r="G491" s="7" t="n">
+        <v>27.11</v>
+      </c>
       <c r="H491" s="7" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="I491" s="8" t="n">
-        <v>-0.0775</v>
-      </c>
-      <c r="J491" s="8" t="n">
-        <v>-2.4711</v>
-      </c>
+        <v>0.2536</v>
+      </c>
+      <c r="J491" s="6" t="inlineStr"/>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M491" s="6" t="inlineStr"/>
@@ -21866,42 +21866,42 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>INGRM</t>
         </is>
       </c>
       <c r="B492" s="3" t="n">
-        <v>20.44</v>
+        <v>427</v>
       </c>
       <c r="C492" s="4" t="n">
-        <v>-0.0068</v>
+        <v>0.0289</v>
       </c>
       <c r="D492" s="5" t="n">
-        <v>22250000</v>
+        <v>51020</v>
       </c>
       <c r="E492" s="4" t="n">
-        <v>0.1865</v>
+        <v>0.0842</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>47.29</v>
+        <v>60.8</v>
       </c>
       <c r="G492" s="2" t="inlineStr"/>
       <c r="H492" s="3" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="I492" s="4" t="n">
-        <v>0.0354</v>
+        <v>-0.0775</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>0.7116</v>
+        <v>-2.4711</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L492" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M492" s="2" t="inlineStr"/>
@@ -21909,44 +21909,42 @@
     <row r="493">
       <c r="A493" s="6" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="B493" s="7" t="n">
-        <v>107</v>
+        <v>20.44</v>
       </c>
       <c r="C493" s="8" t="n">
-        <v>-0.0019</v>
+        <v>-0.0068</v>
       </c>
       <c r="D493" s="9" t="n">
-        <v>8730000</v>
+        <v>22250000</v>
       </c>
       <c r="E493" s="8" t="n">
-        <v>0.1466</v>
+        <v>0.1865</v>
       </c>
       <c r="F493" s="7" t="n">
-        <v>35.09</v>
-      </c>
-      <c r="G493" s="7" t="n">
-        <v>65.2</v>
-      </c>
+        <v>47.29</v>
+      </c>
+      <c r="G493" s="6" t="inlineStr"/>
       <c r="H493" s="7" t="n">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="I493" s="8" t="n">
-        <v>0.096</v>
+        <v>0.0354</v>
       </c>
       <c r="J493" s="8" t="n">
-        <v>2.6213</v>
+        <v>0.7116</v>
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M493" s="6" t="inlineStr"/>
@@ -21954,42 +21952,44 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>OTKAR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B494" s="3" t="n">
-        <v>384</v>
+        <v>107</v>
       </c>
       <c r="C494" s="4" t="n">
-        <v>-0.0185</v>
+        <v>-0.0019</v>
       </c>
       <c r="D494" s="5" t="n">
-        <v>784530</v>
+        <v>8730000</v>
       </c>
       <c r="E494" s="4" t="n">
-        <v>0.2781</v>
+        <v>0.1466</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="G494" s="2" t="inlineStr"/>
+        <v>35.09</v>
+      </c>
+      <c r="G494" s="3" t="n">
+        <v>65.2</v>
+      </c>
       <c r="H494" s="3" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="I494" s="4" t="n">
-        <v>-0.1702</v>
+        <v>0.096</v>
       </c>
       <c r="J494" s="4" t="n">
-        <v>-1.9167</v>
+        <v>2.6213</v>
       </c>
       <c r="K494" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L494" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M494" s="2" t="inlineStr"/>
@@ -21997,42 +21997,42 @@
     <row r="495">
       <c r="A495" s="6" t="inlineStr">
         <is>
-          <t>BAYRK</t>
+          <t>OTKAR</t>
         </is>
       </c>
       <c r="B495" s="7" t="n">
-        <v>4.8</v>
+        <v>384</v>
       </c>
       <c r="C495" s="8" t="n">
-        <v>-0.0244</v>
+        <v>-0.0185</v>
       </c>
       <c r="D495" s="9" t="n">
-        <v>18270000</v>
+        <v>784530</v>
       </c>
       <c r="E495" s="8" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.2781</v>
       </c>
       <c r="F495" s="7" t="n">
-        <v>51.76</v>
+        <v>46.95</v>
       </c>
       <c r="G495" s="6" t="inlineStr"/>
       <c r="H495" s="7" t="n">
-        <v>5.66</v>
+        <v>5.39</v>
       </c>
       <c r="I495" s="8" t="n">
-        <v>-1.1206</v>
+        <v>-0.1702</v>
       </c>
       <c r="J495" s="8" t="n">
-        <v>-7.040900000000001</v>
+        <v>-1.9167</v>
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOBİ SANAYİ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M495" s="6" t="inlineStr"/>
@@ -22040,44 +22040,42 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>BAYRK</t>
         </is>
       </c>
       <c r="B496" s="3" t="n">
-        <v>516.5</v>
+        <v>4.8</v>
       </c>
       <c r="C496" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0244</v>
       </c>
       <c r="D496" s="5" t="n">
-        <v>2220000</v>
+        <v>18270000</v>
       </c>
       <c r="E496" s="4" t="n">
-        <v>0.2127</v>
+        <v>0.9651000000000001</v>
       </c>
       <c r="F496" s="3" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="G496" s="3" t="n">
-        <v>31.62</v>
-      </c>
+        <v>51.76</v>
+      </c>
+      <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="3" t="n">
-        <v>5.75</v>
+        <v>5.66</v>
       </c>
       <c r="I496" s="4" t="n">
-        <v>0.2409</v>
+        <v>-1.1206</v>
       </c>
       <c r="J496" s="4" t="n">
-        <v>-0.336</v>
+        <v>-7.040900000000001</v>
       </c>
       <c r="K496" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L496" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOBİ SANAYİ</t>
         </is>
       </c>
       <c r="M496" s="2" t="inlineStr"/>
@@ -22085,42 +22083,44 @@
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
         <is>
-          <t>EUKYO</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B497" s="7" t="n">
-        <v>7.61</v>
+        <v>516.5</v>
       </c>
       <c r="C497" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D497" s="9" t="n">
-        <v>1030000</v>
+        <v>2220000</v>
       </c>
       <c r="E497" s="8" t="n">
-        <v>0.2908</v>
+        <v>0.2127</v>
       </c>
       <c r="F497" s="7" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="G497" s="6" t="inlineStr"/>
+        <v>55.41</v>
+      </c>
+      <c r="G497" s="7" t="n">
+        <v>31.62</v>
+      </c>
       <c r="H497" s="7" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="I497" s="8" t="n">
-        <v>-0.2463</v>
+        <v>0.2409</v>
       </c>
       <c r="J497" s="8" t="n">
-        <v>0.0757</v>
+        <v>-0.336</v>
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
         </is>
       </c>
       <c r="M497" s="6" t="inlineStr"/>
@@ -22128,44 +22128,42 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>MACKO</t>
+          <t>EUKYO</t>
         </is>
       </c>
       <c r="B498" s="3" t="n">
-        <v>41.4</v>
+        <v>7.61</v>
       </c>
       <c r="C498" s="4" t="n">
-        <v>0.0122</v>
+        <v>0.0425</v>
       </c>
       <c r="D498" s="5" t="n">
-        <v>3230000</v>
+        <v>1030000</v>
       </c>
       <c r="E498" s="4" t="n">
-        <v>0.3124</v>
+        <v>0.2908</v>
       </c>
       <c r="F498" s="3" t="n">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="G498" s="3" t="n">
-        <v>13.65</v>
-      </c>
+        <v>64.34</v>
+      </c>
+      <c r="G498" s="2" t="inlineStr"/>
       <c r="H498" s="3" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
       <c r="I498" s="4" t="n">
-        <v>0.5293</v>
+        <v>-0.2463</v>
       </c>
       <c r="J498" s="4" t="n">
-        <v>-0.4614</v>
+        <v>0.0757</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L498" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M498" s="2" t="inlineStr"/>
@@ -22173,42 +22171,44 @@
     <row r="499">
       <c r="A499" s="6" t="inlineStr">
         <is>
-          <t>DITAS</t>
+          <t>MACKO</t>
         </is>
       </c>
       <c r="B499" s="7" t="n">
-        <v>33.74</v>
+        <v>41.4</v>
       </c>
       <c r="C499" s="8" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="D499" s="7" t="n">
-        <v>2090000</v>
+        <v>0.0122</v>
+      </c>
+      <c r="D499" s="9" t="n">
+        <v>3230000</v>
       </c>
       <c r="E499" s="8" t="n">
-        <v>0.6587999999999999</v>
+        <v>0.3124</v>
       </c>
       <c r="F499" s="7" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G499" s="6" t="inlineStr"/>
+        <v>69.73999999999999</v>
+      </c>
+      <c r="G499" s="7" t="n">
+        <v>13.65</v>
+      </c>
       <c r="H499" s="7" t="n">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="I499" s="8" t="n">
-        <v>-0.6823</v>
+        <v>0.5293</v>
       </c>
       <c r="J499" s="8" t="n">
-        <v>-2.0132</v>
+        <v>-0.4614</v>
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M499" s="6" t="inlineStr"/>
@@ -22216,44 +22216,42 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>CLEBI</t>
-        </is>
-      </c>
-      <c r="B500" s="5" t="n">
-        <v>2099</v>
+          <t>DITAS</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="n">
+        <v>33.74</v>
       </c>
       <c r="C500" s="4" t="n">
-        <v>-0.0127</v>
-      </c>
-      <c r="D500" s="5" t="n">
-        <v>123070</v>
+        <v>0.0224</v>
+      </c>
+      <c r="D500" s="3" t="n">
+        <v>2090000</v>
       </c>
       <c r="E500" s="4" t="n">
-        <v>0.1009</v>
+        <v>0.6587999999999999</v>
       </c>
       <c r="F500" s="3" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="G500" s="3" t="n">
-        <v>14.02</v>
-      </c>
+        <v>39.1</v>
+      </c>
+      <c r="G500" s="2" t="inlineStr"/>
       <c r="H500" s="3" t="n">
-        <v>6.08</v>
+        <v>6.05</v>
       </c>
       <c r="I500" s="4" t="n">
-        <v>0.4328</v>
+        <v>-0.6823</v>
       </c>
       <c r="J500" s="4" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-2.0132</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L500" s="2" t="inlineStr">
         <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA</t>
         </is>
       </c>
       <c r="M500" s="2" t="inlineStr"/>
@@ -22261,44 +22259,44 @@
     <row r="501">
       <c r="A501" s="6" t="inlineStr">
         <is>
-          <t>TEHOL</t>
-        </is>
-      </c>
-      <c r="B501" s="7" t="n">
-        <v>24.98</v>
+          <t>CLEBI</t>
+        </is>
+      </c>
+      <c r="B501" s="9" t="n">
+        <v>2099</v>
       </c>
       <c r="C501" s="8" t="n">
-        <v>-0.015</v>
+        <v>-0.0127</v>
       </c>
       <c r="D501" s="9" t="n">
-        <v>223950000</v>
+        <v>123070</v>
       </c>
       <c r="E501" s="8" t="n">
-        <v>0.7476999999999999</v>
+        <v>0.1009</v>
       </c>
       <c r="F501" s="7" t="n">
-        <v>77.55</v>
+        <v>66.75</v>
       </c>
       <c r="G501" s="7" t="n">
-        <v>17.98</v>
+        <v>14.02</v>
       </c>
       <c r="H501" s="7" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
       <c r="I501" s="8" t="n">
-        <v>0.5092</v>
+        <v>0.4328</v>
       </c>
       <c r="J501" s="8" t="n">
-        <v>-0.9779000000000001</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M501" s="6" t="inlineStr"/>
@@ -22306,44 +22304,44 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
-        <v>288.25</v>
+        <v>24.98</v>
       </c>
       <c r="C502" s="4" t="n">
-        <v>-0.0077</v>
+        <v>-0.015</v>
       </c>
       <c r="D502" s="5" t="n">
-        <v>94960</v>
+        <v>223950000</v>
       </c>
       <c r="E502" s="4" t="n">
-        <v>0.2226</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="F502" s="3" t="n">
-        <v>49.61</v>
+        <v>77.55</v>
       </c>
       <c r="G502" s="3" t="n">
-        <v>56.62</v>
+        <v>17.98</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="I502" s="4" t="n">
-        <v>0.1315</v>
+        <v>0.5092</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>-0.4854</v>
+        <v>-0.9779000000000001</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L502" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M502" s="2" t="inlineStr"/>
@@ -22351,44 +22349,44 @@
     <row r="503">
       <c r="A503" s="6" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B503" s="7" t="n">
-        <v>289</v>
+        <v>288.25</v>
       </c>
       <c r="C503" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0077</v>
       </c>
       <c r="D503" s="9" t="n">
-        <v>5790000</v>
+        <v>94960</v>
       </c>
       <c r="E503" s="8" t="n">
-        <v>0.3143</v>
+        <v>0.2226</v>
       </c>
       <c r="F503" s="7" t="n">
-        <v>34.44</v>
+        <v>49.61</v>
       </c>
       <c r="G503" s="7" t="n">
-        <v>5.67</v>
+        <v>56.62</v>
       </c>
       <c r="H503" s="7" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="I503" s="8" t="n">
-        <v>2.2403</v>
+        <v>0.1315</v>
       </c>
       <c r="J503" s="8" t="n">
-        <v>-0.7998000000000001</v>
+        <v>-0.4854</v>
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M503" s="6" t="inlineStr"/>
@@ -22396,35 +22394,35 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
-        <v>30.16</v>
+        <v>289</v>
       </c>
       <c r="C504" s="4" t="n">
-        <v>0.0033</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D504" s="5" t="n">
-        <v>2740000</v>
+        <v>5790000</v>
       </c>
       <c r="E504" s="4" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.3143</v>
       </c>
       <c r="F504" s="3" t="n">
-        <v>66.16</v>
+        <v>34.44</v>
       </c>
       <c r="G504" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>5.67</v>
       </c>
       <c r="H504" s="3" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="I504" s="4" t="n">
-        <v>0.9309000000000001</v>
+        <v>2.2403</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>2.8984</v>
+        <v>-0.7998000000000001</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -22433,7 +22431,7 @@
       </c>
       <c r="L504" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M504" s="2" t="inlineStr"/>
@@ -22441,42 +22439,44 @@
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
         <is>
-          <t>BIGTK</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B505" s="7" t="n">
-        <v>214.3</v>
+        <v>30.16</v>
       </c>
       <c r="C505" s="8" t="n">
-        <v>-0.0124</v>
+        <v>0.0033</v>
       </c>
       <c r="D505" s="9" t="n">
-        <v>421660</v>
+        <v>2740000</v>
       </c>
       <c r="E505" s="8" t="n">
-        <v>0.2138</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="F505" s="7" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="G505" s="6" t="inlineStr"/>
+        <v>66.16</v>
+      </c>
+      <c r="G505" s="7" t="n">
+        <v>9.869999999999999</v>
+      </c>
       <c r="H505" s="7" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="I505" s="8" t="n">
-        <v>-0.1167</v>
+        <v>0.9309000000000001</v>
       </c>
       <c r="J505" s="8" t="n">
-        <v>0.0278</v>
+        <v>2.8984</v>
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M505" s="6" t="inlineStr"/>
@@ -22484,44 +22484,42 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>BIGTK</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
-        <v>207.9</v>
+        <v>214.3</v>
       </c>
       <c r="C506" s="4" t="n">
-        <v>-0.0308</v>
+        <v>-0.0124</v>
       </c>
       <c r="D506" s="5" t="n">
-        <v>40610000</v>
+        <v>421660</v>
       </c>
       <c r="E506" s="4" t="n">
-        <v>0.317</v>
+        <v>0.2138</v>
       </c>
       <c r="F506" s="3" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="G506" s="3" t="n">
-        <v>27.76</v>
-      </c>
+        <v>39.25</v>
+      </c>
+      <c r="G506" s="2" t="inlineStr"/>
       <c r="H506" s="3" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="I506" s="4" t="n">
-        <v>0.2763</v>
+        <v>-0.1167</v>
       </c>
       <c r="J506" s="4" t="n">
-        <v>0.0601</v>
+        <v>0.0278</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L506" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M506" s="2" t="inlineStr"/>
@@ -22529,42 +22527,44 @@
     <row r="507">
       <c r="A507" s="6" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B507" s="7" t="n">
-        <v>124.6</v>
+        <v>207.9</v>
       </c>
       <c r="C507" s="8" t="n">
-        <v>-0.0166</v>
+        <v>-0.0308</v>
       </c>
       <c r="D507" s="9" t="n">
-        <v>8780000</v>
+        <v>40610000</v>
       </c>
       <c r="E507" s="8" t="n">
-        <v>0.3148</v>
+        <v>0.317</v>
       </c>
       <c r="F507" s="7" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="G507" s="6" t="inlineStr"/>
+        <v>56.33</v>
+      </c>
+      <c r="G507" s="7" t="n">
+        <v>27.76</v>
+      </c>
       <c r="H507" s="7" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="I507" s="8" t="n">
-        <v>0.3692</v>
+        <v>0.2763</v>
       </c>
       <c r="J507" s="8" t="n">
-        <v>0.507</v>
+        <v>0.0601</v>
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M507" s="6" t="inlineStr"/>
@@ -22572,44 +22572,42 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
-        <v>145</v>
+        <v>124.6</v>
       </c>
       <c r="C508" s="4" t="n">
-        <v>0.0387</v>
+        <v>-0.0166</v>
       </c>
       <c r="D508" s="5" t="n">
-        <v>1580000</v>
+        <v>8780000</v>
       </c>
       <c r="E508" s="4" t="n">
-        <v>0.1694</v>
+        <v>0.3148</v>
       </c>
       <c r="F508" s="3" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G508" s="3" t="n">
-        <v>58.47</v>
-      </c>
+        <v>44.07</v>
+      </c>
+      <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="3" t="n">
-        <v>6.37</v>
+        <v>6.26</v>
       </c>
       <c r="I508" s="4" t="n">
-        <v>0.1283</v>
+        <v>0.3692</v>
       </c>
       <c r="J508" s="4" t="n">
-        <v>-0.5074000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="K508" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L508" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
         </is>
       </c>
       <c r="M508" s="2" t="inlineStr"/>
@@ -22617,42 +22615,44 @@
     <row r="509">
       <c r="A509" s="6" t="inlineStr">
         <is>
-          <t>YAPRK</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B509" s="7" t="n">
-        <v>14.88</v>
+        <v>145</v>
       </c>
       <c r="C509" s="8" t="n">
-        <v>-0.0126</v>
+        <v>0.0387</v>
       </c>
       <c r="D509" s="9" t="n">
-        <v>5670000</v>
+        <v>1580000</v>
       </c>
       <c r="E509" s="8" t="n">
-        <v>0.2817</v>
+        <v>0.1694</v>
       </c>
       <c r="F509" s="7" t="n">
-        <v>48.5</v>
+        <v>75.5</v>
       </c>
       <c r="G509" s="7" t="n">
-        <v>200.81</v>
+        <v>58.47</v>
       </c>
       <c r="H509" s="7" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="I509" s="8" t="n">
-        <v>0.0366</v>
-      </c>
-      <c r="J509" s="6" t="inlineStr"/>
+        <v>0.1283</v>
+      </c>
+      <c r="J509" s="8" t="n">
+        <v>-0.5074000000000001</v>
+      </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST TEMETTU, BIST KOBİ SANAYİ, BIST BALIKESİR</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M509" s="6" t="inlineStr"/>
@@ -22660,42 +22660,42 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>INTEM</t>
+          <t>YAPRK</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
-        <v>290</v>
+        <v>14.88</v>
       </c>
       <c r="C510" s="4" t="n">
-        <v>-0.0203</v>
+        <v>-0.0126</v>
       </c>
       <c r="D510" s="5" t="n">
-        <v>139010</v>
+        <v>5670000</v>
       </c>
       <c r="E510" s="4" t="n">
-        <v>0.1268</v>
+        <v>0.2817</v>
       </c>
       <c r="F510" s="3" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="G510" s="2" t="inlineStr"/>
+        <v>48.5</v>
+      </c>
+      <c r="G510" s="3" t="n">
+        <v>200.81</v>
+      </c>
       <c r="H510" s="3" t="n">
-        <v>6.55</v>
+        <v>6.41</v>
       </c>
       <c r="I510" s="4" t="n">
-        <v>-0.0097</v>
-      </c>
-      <c r="J510" s="4" t="n">
-        <v>-3.335</v>
-      </c>
+        <v>0.0366</v>
+      </c>
+      <c r="J510" s="2" t="inlineStr"/>
       <c r="K510" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L510" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST TEMETTU, BIST KOBİ SANAYİ, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M510" s="2" t="inlineStr"/>
@@ -22703,122 +22703,122 @@
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
         <is>
-          <t>SODSN</t>
+          <t>INTEM</t>
         </is>
       </c>
       <c r="B511" s="7" t="n">
-        <v>10</v>
+        <v>290</v>
       </c>
       <c r="C511" s="8" t="n">
-        <v>-0.0291</v>
+        <v>-0.0203</v>
       </c>
       <c r="D511" s="9" t="n">
-        <v>118490</v>
+        <v>139010</v>
       </c>
       <c r="E511" s="8" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.1268</v>
       </c>
       <c r="F511" s="7" t="n">
-        <v>51.81</v>
+        <v>50.34</v>
       </c>
       <c r="G511" s="6" t="inlineStr"/>
       <c r="H511" s="7" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="I511" s="8" t="n">
-        <v>-0.2148</v>
-      </c>
-      <c r="J511" s="6" t="inlineStr"/>
+        <v>-0.0097</v>
+      </c>
+      <c r="J511" s="8" t="n">
+        <v>-3.335</v>
+      </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L511" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L511" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M511" s="6" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>TKNSA</t>
+          <t>SODSN</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
-        <v>23.92</v>
+        <v>10</v>
       </c>
       <c r="C512" s="4" t="n">
-        <v>-0.0545</v>
+        <v>-0.0291</v>
       </c>
       <c r="D512" s="5" t="n">
-        <v>9780000</v>
+        <v>118490</v>
       </c>
       <c r="E512" s="4" t="n">
-        <v>0.4494</v>
+        <v>0.9193000000000001</v>
       </c>
       <c r="F512" s="3" t="n">
-        <v>54.79</v>
+        <v>51.81</v>
       </c>
       <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="3" t="n">
-        <v>6.66</v>
+        <v>6.6</v>
       </c>
       <c r="I512" s="4" t="n">
-        <v>-1.4367</v>
-      </c>
-      <c r="J512" s="4" t="n">
-        <v>-3.178</v>
-      </c>
+        <v>-0.2148</v>
+      </c>
+      <c r="J512" s="2" t="inlineStr"/>
       <c r="K512" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L512" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L512" s="2" t="inlineStr"/>
       <c r="M512" s="2" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
         <is>
-          <t>KAREL</t>
+          <t>TKNSA</t>
         </is>
       </c>
       <c r="B513" s="7" t="n">
-        <v>10.56</v>
+        <v>23.92</v>
       </c>
       <c r="C513" s="8" t="n">
-        <v>-0.0158</v>
+        <v>-0.0545</v>
       </c>
       <c r="D513" s="9" t="n">
-        <v>13840000</v>
+        <v>9780000</v>
       </c>
       <c r="E513" s="8" t="n">
-        <v>0.4395</v>
+        <v>0.4494</v>
       </c>
       <c r="F513" s="7" t="n">
-        <v>67.59</v>
+        <v>54.79</v>
       </c>
       <c r="G513" s="6" t="inlineStr"/>
       <c r="H513" s="7" t="n">
-        <v>6.71</v>
+        <v>6.66</v>
       </c>
       <c r="I513" s="8" t="n">
-        <v>-0.9031999999999999</v>
+        <v>-1.4367</v>
       </c>
       <c r="J513" s="8" t="n">
-        <v>0.8837999999999999</v>
+        <v>-3.178</v>
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M513" s="6" t="inlineStr"/>
@@ -22826,42 +22826,42 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>AYCES</t>
-        </is>
-      </c>
-      <c r="B514" s="5" t="n">
-        <v>1305</v>
+          <t>KAREL</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="n">
+        <v>10.56</v>
       </c>
       <c r="C514" s="4" t="n">
-        <v>0.0077</v>
+        <v>-0.0158</v>
       </c>
       <c r="D514" s="5" t="n">
-        <v>232980</v>
+        <v>13840000</v>
       </c>
       <c r="E514" s="4" t="n">
-        <v>0.0814</v>
+        <v>0.4395</v>
       </c>
       <c r="F514" s="3" t="n">
-        <v>87.77</v>
+        <v>67.59</v>
       </c>
       <c r="G514" s="2" t="inlineStr"/>
       <c r="H514" s="3" t="n">
-        <v>6.8</v>
+        <v>6.71</v>
       </c>
       <c r="I514" s="4" t="n">
-        <v>-0.016</v>
+        <v>-0.9031999999999999</v>
       </c>
       <c r="J514" s="4" t="n">
-        <v>-2.6951</v>
+        <v>0.8837999999999999</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L514" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
         </is>
       </c>
       <c r="M514" s="2" t="inlineStr"/>
@@ -22869,40 +22869,42 @@
     <row r="515">
       <c r="A515" s="6" t="inlineStr">
         <is>
-          <t>BIZIM</t>
-        </is>
-      </c>
-      <c r="B515" s="7" t="n">
-        <v>28.32</v>
+          <t>AYCES</t>
+        </is>
+      </c>
+      <c r="B515" s="9" t="n">
+        <v>1305</v>
       </c>
       <c r="C515" s="8" t="n">
-        <v>-0.0119</v>
+        <v>0.0077</v>
       </c>
       <c r="D515" s="9" t="n">
-        <v>392170</v>
+        <v>232980</v>
       </c>
       <c r="E515" s="8" t="n">
-        <v>0.3341</v>
+        <v>0.0814</v>
       </c>
       <c r="F515" s="7" t="n">
-        <v>58.51</v>
+        <v>87.77</v>
       </c>
       <c r="G515" s="6" t="inlineStr"/>
       <c r="H515" s="7" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="I515" s="8" t="n">
-        <v>-1.089</v>
-      </c>
-      <c r="J515" s="6" t="inlineStr"/>
+        <v>-0.016</v>
+      </c>
+      <c r="J515" s="8" t="n">
+        <v>-2.6951</v>
+      </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M515" s="6" t="inlineStr"/>
@@ -22910,40 +22912,40 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>PAPIL</t>
+          <t>BIZIM</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
-        <v>17.3</v>
+        <v>28.32</v>
       </c>
       <c r="C516" s="4" t="n">
-        <v>0.0328</v>
+        <v>-0.0119</v>
       </c>
       <c r="D516" s="5" t="n">
-        <v>23000000</v>
+        <v>392170</v>
       </c>
       <c r="E516" s="4" t="n">
-        <v>0.8020999999999999</v>
+        <v>0.3341</v>
       </c>
       <c r="F516" s="3" t="n">
-        <v>57.33</v>
+        <v>58.51</v>
       </c>
       <c r="G516" s="2" t="inlineStr"/>
       <c r="H516" s="3" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="I516" s="2" t="inlineStr"/>
-      <c r="J516" s="4" t="n">
-        <v>-0.9567</v>
-      </c>
+        <v>6.83</v>
+      </c>
+      <c r="I516" s="4" t="n">
+        <v>-1.089</v>
+      </c>
+      <c r="J516" s="2" t="inlineStr"/>
       <c r="K516" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L516" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK</t>
         </is>
       </c>
       <c r="M516" s="2" t="inlineStr"/>
@@ -22951,42 +22953,40 @@
     <row r="517">
       <c r="A517" s="6" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>PAPIL</t>
         </is>
       </c>
       <c r="B517" s="7" t="n">
-        <v>54.15</v>
+        <v>17.3</v>
       </c>
       <c r="C517" s="8" t="n">
-        <v>-0.0181</v>
+        <v>0.0328</v>
       </c>
       <c r="D517" s="9" t="n">
-        <v>148950</v>
-      </c>
-      <c r="E517" s="6" t="inlineStr"/>
+        <v>23000000</v>
+      </c>
+      <c r="E517" s="8" t="n">
+        <v>0.8020999999999999</v>
+      </c>
       <c r="F517" s="7" t="n">
-        <v>43.27</v>
-      </c>
-      <c r="G517" s="7" t="n">
-        <v>152.62</v>
-      </c>
+        <v>57.33</v>
+      </c>
+      <c r="G517" s="6" t="inlineStr"/>
       <c r="H517" s="7" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="I517" s="8" t="n">
-        <v>0.05309999999999999</v>
-      </c>
+        <v>6.97</v>
+      </c>
+      <c r="I517" s="6" t="inlineStr"/>
       <c r="J517" s="8" t="n">
-        <v>1.1582</v>
+        <v>-0.9567</v>
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
         </is>
       </c>
       <c r="M517" s="6" t="inlineStr"/>
@@ -22994,44 +22994,42 @@
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">
-        <v>396.5</v>
+        <v>54.15</v>
       </c>
       <c r="C518" s="4" t="n">
-        <v>0</v>
+        <v>-0.0181</v>
       </c>
       <c r="D518" s="5" t="n">
-        <v>29290000</v>
-      </c>
-      <c r="E518" s="4" t="n">
-        <v>0.258</v>
-      </c>
+        <v>148950</v>
+      </c>
+      <c r="E518" s="2" t="inlineStr"/>
       <c r="F518" s="3" t="n">
-        <v>62.55</v>
+        <v>43.27</v>
       </c>
       <c r="G518" s="3" t="n">
-        <v>61.64</v>
+        <v>152.62</v>
       </c>
       <c r="H518" s="3" t="n">
-        <v>7.22</v>
+        <v>7.02</v>
       </c>
       <c r="I518" s="4" t="n">
-        <v>0.1501</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="J518" s="4" t="n">
-        <v>2.84</v>
+        <v>1.1582</v>
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L518" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST 50, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M518" s="2" t="inlineStr"/>
@@ -23039,42 +23037,44 @@
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B519" s="7" t="n">
-        <v>76.84999999999999</v>
+        <v>396.5</v>
       </c>
       <c r="C519" s="8" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="D519" s="9" t="n">
-        <v>4740000</v>
+        <v>29290000</v>
       </c>
       <c r="E519" s="8" t="n">
-        <v>0.2346</v>
+        <v>0.258</v>
       </c>
       <c r="F519" s="7" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="G519" s="6" t="inlineStr"/>
+        <v>62.55</v>
+      </c>
+      <c r="G519" s="7" t="n">
+        <v>61.64</v>
+      </c>
       <c r="H519" s="7" t="n">
-        <v>7.28</v>
+        <v>7.22</v>
       </c>
       <c r="I519" s="8" t="n">
-        <v>-0.1254</v>
+        <v>0.1501</v>
       </c>
       <c r="J519" s="8" t="n">
-        <v>-7.7801</v>
+        <v>2.84</v>
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ, BIST BALIKESİR</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST 50, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M519" s="6" t="inlineStr"/>
@@ -23082,40 +23082,42 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>ETYAT</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="B520" s="3" t="n">
-        <v>8.24</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C520" s="4" t="n">
-        <v>0.0135</v>
+        <v>0.0159</v>
       </c>
       <c r="D520" s="5" t="n">
-        <v>930860</v>
-      </c>
-      <c r="E520" s="2" t="inlineStr"/>
+        <v>4740000</v>
+      </c>
+      <c r="E520" s="4" t="n">
+        <v>0.2346</v>
+      </c>
       <c r="F520" s="3" t="n">
-        <v>65.01000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="G520" s="2" t="inlineStr"/>
       <c r="H520" s="3" t="n">
-        <v>7.39</v>
+        <v>7.28</v>
       </c>
       <c r="I520" s="4" t="n">
-        <v>-0.2944</v>
+        <v>-0.1254</v>
       </c>
       <c r="J520" s="4" t="n">
-        <v>-0.6470999999999999</v>
+        <v>-7.7801</v>
       </c>
       <c r="K520" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L520" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M520" s="2" t="inlineStr"/>
@@ -23123,44 +23125,40 @@
     <row r="521">
       <c r="A521" s="6" t="inlineStr">
         <is>
-          <t>DGATE</t>
+          <t>ETYAT</t>
         </is>
       </c>
       <c r="B521" s="7" t="n">
-        <v>82.25</v>
+        <v>8.24</v>
       </c>
       <c r="C521" s="8" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="D521" s="9" t="n">
-        <v>377840</v>
-      </c>
-      <c r="E521" s="8" t="n">
-        <v>0.4076</v>
-      </c>
+        <v>930860</v>
+      </c>
+      <c r="E521" s="6" t="inlineStr"/>
       <c r="F521" s="7" t="n">
-        <v>67.63</v>
-      </c>
-      <c r="G521" s="7" t="n">
-        <v>112.86</v>
-      </c>
+        <v>65.01000000000001</v>
+      </c>
+      <c r="G521" s="6" t="inlineStr"/>
       <c r="H521" s="7" t="n">
-        <v>7.49</v>
+        <v>7.39</v>
       </c>
       <c r="I521" s="8" t="n">
-        <v>0.077</v>
+        <v>-0.2944</v>
       </c>
       <c r="J521" s="8" t="n">
-        <v>546.9397</v>
+        <v>-0.6470999999999999</v>
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M521" s="6" t="inlineStr"/>
@@ -23168,42 +23166,44 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>VERUS</t>
+          <t>DGATE</t>
         </is>
       </c>
       <c r="B522" s="3" t="n">
-        <v>510</v>
+        <v>82.25</v>
       </c>
       <c r="C522" s="4" t="n">
-        <v>-0.044</v>
+        <v>0</v>
       </c>
       <c r="D522" s="5" t="n">
-        <v>94560</v>
+        <v>377840</v>
       </c>
       <c r="E522" s="4" t="n">
-        <v>0.3633</v>
+        <v>0.4076</v>
       </c>
       <c r="F522" s="3" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="G522" s="2" t="inlineStr"/>
+        <v>67.63</v>
+      </c>
+      <c r="G522" s="3" t="n">
+        <v>112.86</v>
+      </c>
       <c r="H522" s="3" t="n">
-        <v>7.63</v>
+        <v>7.49</v>
       </c>
       <c r="I522" s="4" t="n">
-        <v>-0.07200000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="J522" s="4" t="n">
-        <v>-5.0791</v>
+        <v>546.9397</v>
       </c>
       <c r="K522" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L522" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M522" s="2" t="inlineStr"/>
@@ -23211,42 +23211,42 @@
     <row r="523">
       <c r="A523" s="6" t="inlineStr">
         <is>
-          <t>MZHLD</t>
+          <t>VERUS</t>
         </is>
       </c>
       <c r="B523" s="7" t="n">
-        <v>6.33</v>
+        <v>510</v>
       </c>
       <c r="C523" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.044</v>
       </c>
       <c r="D523" s="9" t="n">
-        <v>644930</v>
+        <v>94560</v>
       </c>
       <c r="E523" s="8" t="n">
-        <v>0.7916</v>
+        <v>0.3633</v>
       </c>
       <c r="F523" s="7" t="n">
-        <v>55.38</v>
+        <v>68.42</v>
       </c>
       <c r="G523" s="6" t="inlineStr"/>
       <c r="H523" s="7" t="n">
-        <v>7.7</v>
+        <v>7.63</v>
       </c>
       <c r="I523" s="8" t="n">
-        <v>-1.4376</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="J523" s="8" t="n">
-        <v>-5.4758</v>
+        <v>-5.0791</v>
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M523" s="6" t="inlineStr"/>
@@ -23254,42 +23254,42 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>MZHLD</t>
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>18.28</v>
+        <v>6.33</v>
       </c>
       <c r="C524" s="4" t="n">
-        <v>0.0218</v>
+        <v>-0.0156</v>
       </c>
       <c r="D524" s="5" t="n">
-        <v>928390</v>
+        <v>644930</v>
       </c>
       <c r="E524" s="4" t="n">
-        <v>0.9869</v>
+        <v>0.7916</v>
       </c>
       <c r="F524" s="3" t="n">
-        <v>69.34999999999999</v>
+        <v>55.38</v>
       </c>
       <c r="G524" s="2" t="inlineStr"/>
       <c r="H524" s="3" t="n">
-        <v>7.73</v>
+        <v>7.7</v>
       </c>
       <c r="I524" s="4" t="n">
-        <v>-0.2375</v>
+        <v>-1.4376</v>
       </c>
       <c r="J524" s="4" t="n">
-        <v>-2.3984</v>
+        <v>-5.4758</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L524" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İZMİR</t>
         </is>
       </c>
       <c r="M524" s="2" t="inlineStr"/>
@@ -23297,42 +23297,42 @@
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
         <is>
-          <t>ENSRI</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B525" s="7" t="n">
-        <v>20.22</v>
+        <v>18.28</v>
       </c>
       <c r="C525" s="8" t="n">
-        <v>-0.0165</v>
+        <v>0.0218</v>
       </c>
       <c r="D525" s="9" t="n">
-        <v>13000000</v>
+        <v>928390</v>
       </c>
       <c r="E525" s="8" t="n">
-        <v>0.4329</v>
+        <v>0.9869</v>
       </c>
       <c r="F525" s="7" t="n">
-        <v>28.9</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="G525" s="6" t="inlineStr"/>
       <c r="H525" s="7" t="n">
-        <v>7.81</v>
+        <v>7.73</v>
       </c>
       <c r="I525" s="8" t="n">
-        <v>-0.0555</v>
+        <v>-0.2375</v>
       </c>
       <c r="J525" s="8" t="n">
-        <v>-10.8224</v>
+        <v>-2.3984</v>
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M525" s="6" t="inlineStr"/>
@@ -23340,42 +23340,42 @@
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>TGSAS</t>
+          <t>ENSRI</t>
         </is>
       </c>
       <c r="B526" s="3" t="n">
-        <v>168.7</v>
+        <v>20.22</v>
       </c>
       <c r="C526" s="4" t="n">
-        <v>0.028</v>
+        <v>-0.0165</v>
       </c>
       <c r="D526" s="5" t="n">
-        <v>289910</v>
-      </c>
-      <c r="E526" s="2" t="inlineStr"/>
+        <v>13000000</v>
+      </c>
+      <c r="E526" s="4" t="n">
+        <v>0.4329</v>
+      </c>
       <c r="F526" s="3" t="n">
-        <v>53.18</v>
-      </c>
-      <c r="G526" s="3" t="n">
-        <v>29.1</v>
-      </c>
+        <v>28.9</v>
+      </c>
+      <c r="G526" s="2" t="inlineStr"/>
       <c r="H526" s="3" t="n">
         <v>7.81</v>
       </c>
       <c r="I526" s="4" t="n">
-        <v>0.316</v>
+        <v>-0.0555</v>
       </c>
       <c r="J526" s="4" t="n">
-        <v>0.8517</v>
+        <v>-10.8224</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L526" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M526" s="2" t="inlineStr"/>
@@ -23383,42 +23383,42 @@
     <row r="527">
       <c r="A527" s="6" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>TGSAS</t>
         </is>
       </c>
       <c r="B527" s="7" t="n">
-        <v>18.02</v>
+        <v>168.7</v>
       </c>
       <c r="C527" s="8" t="n">
-        <v>-0.0999</v>
+        <v>0.028</v>
       </c>
       <c r="D527" s="9" t="n">
-        <v>3910000</v>
-      </c>
-      <c r="E527" s="8" t="n">
-        <v>0.3615</v>
-      </c>
+        <v>289910</v>
+      </c>
+      <c r="E527" s="6" t="inlineStr"/>
       <c r="F527" s="7" t="n">
-        <v>48.95</v>
-      </c>
-      <c r="G527" s="6" t="inlineStr"/>
+        <v>53.18</v>
+      </c>
+      <c r="G527" s="7" t="n">
+        <v>29.1</v>
+      </c>
       <c r="H527" s="7" t="n">
-        <v>8.130000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="I527" s="8" t="n">
-        <v>-0.0173</v>
+        <v>0.316</v>
       </c>
       <c r="J527" s="8" t="n">
-        <v>-59.0748</v>
+        <v>0.8517</v>
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M527" s="6" t="inlineStr"/>
@@ -23426,128 +23426,128 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>QNBTR</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="B528" s="3" t="n">
-        <v>260.5</v>
+        <v>18.02</v>
       </c>
       <c r="C528" s="4" t="n">
-        <v>-0.0188</v>
+        <v>-0.0999</v>
       </c>
       <c r="D528" s="5" t="n">
-        <v>41700</v>
+        <v>3910000</v>
       </c>
       <c r="E528" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.3615</v>
       </c>
       <c r="F528" s="3" t="n">
-        <v>42.02</v>
-      </c>
-      <c r="G528" s="3" t="n">
-        <v>29.96</v>
-      </c>
+        <v>48.95</v>
+      </c>
+      <c r="G528" s="2" t="inlineStr"/>
       <c r="H528" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I528" s="4" t="n">
-        <v>0.3276</v>
+        <v>-0.0173</v>
       </c>
       <c r="J528" s="4" t="n">
-        <v>0.1497</v>
+        <v>-59.0748</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L528" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+        </is>
+      </c>
       <c r="M528" s="2" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="6" t="inlineStr">
         <is>
-          <t>RODRG</t>
+          <t>QNBTR</t>
         </is>
       </c>
       <c r="B529" s="7" t="n">
-        <v>20.5</v>
+        <v>260.5</v>
       </c>
       <c r="C529" s="8" t="n">
-        <v>-0.001</v>
+        <v>-0.0188</v>
       </c>
       <c r="D529" s="9" t="n">
-        <v>389900</v>
+        <v>41700</v>
       </c>
       <c r="E529" s="8" t="n">
-        <v>0.3225</v>
+        <v>0.0012</v>
       </c>
       <c r="F529" s="7" t="n">
-        <v>50.55</v>
+        <v>42.02</v>
       </c>
       <c r="G529" s="7" t="n">
-        <v>140.6</v>
+        <v>29.96</v>
       </c>
       <c r="H529" s="7" t="n">
-        <v>8.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I529" s="8" t="n">
-        <v>0.0607</v>
+        <v>0.3276</v>
       </c>
       <c r="J529" s="8" t="n">
-        <v>-0.9726</v>
+        <v>0.1497</v>
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L529" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L529" s="6" t="inlineStr"/>
       <c r="M529" s="6" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>OZRDN</t>
+          <t>RODRG</t>
         </is>
       </c>
       <c r="B530" s="3" t="n">
-        <v>37.5</v>
+        <v>20.5</v>
       </c>
       <c r="C530" s="4" t="n">
-        <v>-0.0021</v>
+        <v>-0.001</v>
       </c>
       <c r="D530" s="5" t="n">
-        <v>632750</v>
+        <v>389900</v>
       </c>
       <c r="E530" s="4" t="n">
-        <v>0.3314</v>
+        <v>0.3225</v>
       </c>
       <c r="F530" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G530" s="2" t="inlineStr"/>
+        <v>50.55</v>
+      </c>
+      <c r="G530" s="3" t="n">
+        <v>140.6</v>
+      </c>
       <c r="H530" s="3" t="n">
-        <v>8.48</v>
+        <v>8.35</v>
       </c>
       <c r="I530" s="4" t="n">
-        <v>-0.1812</v>
+        <v>0.0607</v>
       </c>
       <c r="J530" s="4" t="n">
-        <v>0.1259</v>
+        <v>-0.9726</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L530" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
         </is>
       </c>
       <c r="M530" s="2" t="inlineStr"/>
@@ -23555,42 +23555,42 @@
     <row r="531">
       <c r="A531" s="6" t="inlineStr">
         <is>
-          <t>LYDYE</t>
-        </is>
-      </c>
-      <c r="B531" s="9" t="n">
-        <v>16035</v>
+          <t>OZRDN</t>
+        </is>
+      </c>
+      <c r="B531" s="7" t="n">
+        <v>37.5</v>
       </c>
       <c r="C531" s="8" t="n">
-        <v>0.0066</v>
+        <v>-0.0021</v>
       </c>
       <c r="D531" s="9" t="n">
-        <v>2100</v>
+        <v>632750</v>
       </c>
       <c r="E531" s="8" t="n">
-        <v>0.2861</v>
+        <v>0.3314</v>
       </c>
       <c r="F531" s="7" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="G531" s="7" t="n">
-        <v>13.74</v>
-      </c>
+        <v>62.9</v>
+      </c>
+      <c r="G531" s="6" t="inlineStr"/>
       <c r="H531" s="7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="I531" s="8" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="J531" s="6" t="inlineStr"/>
+        <v>-0.1812</v>
+      </c>
+      <c r="J531" s="8" t="n">
+        <v>0.1259</v>
+      </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M531" s="6" t="inlineStr"/>
@@ -23598,42 +23598,42 @@
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>CMBTN</t>
+          <t>LYDYE</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
-        <v>1880</v>
+        <v>16035</v>
       </c>
       <c r="C532" s="4" t="n">
-        <v>0.0113</v>
+        <v>0.0066</v>
       </c>
       <c r="D532" s="5" t="n">
-        <v>43170</v>
+        <v>2100</v>
       </c>
       <c r="E532" s="4" t="n">
-        <v>0.4972</v>
+        <v>0.2861</v>
       </c>
       <c r="F532" s="3" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="G532" s="2" t="inlineStr"/>
+        <v>45.83</v>
+      </c>
+      <c r="G532" s="3" t="n">
+        <v>13.74</v>
+      </c>
       <c r="H532" s="3" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I532" s="4" t="n">
-        <v>-0.6124000000000001</v>
-      </c>
-      <c r="J532" s="4" t="n">
-        <v>-12.8747</v>
-      </c>
+        <v>0.794</v>
+      </c>
+      <c r="J532" s="2" t="inlineStr"/>
       <c r="K532" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L532" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M532" s="2" t="inlineStr"/>
@@ -23641,42 +23641,42 @@
     <row r="533">
       <c r="A533" s="6" t="inlineStr">
         <is>
-          <t>KAPLM</t>
-        </is>
-      </c>
-      <c r="B533" s="7" t="n">
-        <v>621.5</v>
+          <t>CMBTN</t>
+        </is>
+      </c>
+      <c r="B533" s="9" t="n">
+        <v>1880</v>
       </c>
       <c r="C533" s="8" t="n">
-        <v>-0.008</v>
+        <v>0.0113</v>
       </c>
       <c r="D533" s="9" t="n">
-        <v>376400</v>
+        <v>43170</v>
       </c>
       <c r="E533" s="8" t="n">
-        <v>0.222</v>
+        <v>0.4972</v>
       </c>
       <c r="F533" s="7" t="n">
-        <v>64.16</v>
+        <v>64.89</v>
       </c>
       <c r="G533" s="6" t="inlineStr"/>
       <c r="H533" s="7" t="n">
-        <v>8.789999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="I533" s="8" t="n">
-        <v>-0.3331</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J533" s="8" t="n">
-        <v>-0.6662</v>
+        <v>-12.8747</v>
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M533" s="6" t="inlineStr"/>
@@ -23684,42 +23684,42 @@
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>KAPLM</t>
         </is>
       </c>
       <c r="B534" s="3" t="n">
-        <v>43.74</v>
+        <v>621.5</v>
       </c>
       <c r="C534" s="4" t="n">
-        <v>-0.0512</v>
+        <v>-0.008</v>
       </c>
       <c r="D534" s="5" t="n">
-        <v>8320000</v>
+        <v>376400</v>
       </c>
       <c r="E534" s="4" t="n">
-        <v>0.9159999999999999</v>
+        <v>0.222</v>
       </c>
       <c r="F534" s="3" t="n">
-        <v>56.56</v>
+        <v>64.16</v>
       </c>
       <c r="G534" s="2" t="inlineStr"/>
       <c r="H534" s="3" t="n">
-        <v>9.35</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I534" s="4" t="n">
-        <v>-0.3587</v>
+        <v>-0.3331</v>
       </c>
       <c r="J534" s="4" t="n">
-        <v>-9.0931</v>
+        <v>-0.6662</v>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L534" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M534" s="2" t="inlineStr"/>
@@ -23727,42 +23727,42 @@
     <row r="535">
       <c r="A535" s="6" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B535" s="7" t="n">
-        <v>11.43</v>
+        <v>43.74</v>
       </c>
       <c r="C535" s="8" t="n">
-        <v>0.0205</v>
+        <v>-0.0512</v>
       </c>
       <c r="D535" s="9" t="n">
-        <v>23200000</v>
+        <v>8320000</v>
       </c>
       <c r="E535" s="8" t="n">
-        <v>0.3536</v>
+        <v>0.9159999999999999</v>
       </c>
       <c r="F535" s="7" t="n">
-        <v>74.44</v>
+        <v>56.56</v>
       </c>
       <c r="G535" s="6" t="inlineStr"/>
       <c r="H535" s="7" t="n">
-        <v>9.4</v>
+        <v>9.35</v>
       </c>
       <c r="I535" s="8" t="n">
-        <v>-0.555</v>
+        <v>-0.3587</v>
       </c>
       <c r="J535" s="8" t="n">
-        <v>-6.502000000000001</v>
+        <v>-9.0931</v>
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M535" s="6" t="inlineStr"/>
@@ -23770,42 +23770,42 @@
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>KUVVA</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="B536" s="3" t="n">
-        <v>119.6</v>
+        <v>11.43</v>
       </c>
       <c r="C536" s="4" t="n">
-        <v>-0.005</v>
+        <v>0.0205</v>
       </c>
       <c r="D536" s="5" t="n">
-        <v>103540</v>
+        <v>23200000</v>
       </c>
       <c r="E536" s="4" t="n">
-        <v>0.8597</v>
+        <v>0.3536</v>
       </c>
       <c r="F536" s="3" t="n">
-        <v>41.96</v>
+        <v>74.44</v>
       </c>
       <c r="G536" s="2" t="inlineStr"/>
       <c r="H536" s="3" t="n">
-        <v>9.49</v>
+        <v>9.4</v>
       </c>
       <c r="I536" s="4" t="n">
-        <v>-0.3487</v>
+        <v>-0.555</v>
       </c>
       <c r="J536" s="4" t="n">
-        <v>-9.398999999999999</v>
+        <v>-6.502000000000001</v>
       </c>
       <c r="K536" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L536" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M536" s="2" t="inlineStr"/>
@@ -23813,42 +23813,42 @@
     <row r="537">
       <c r="A537" s="6" t="inlineStr">
         <is>
-          <t>BMSTL</t>
+          <t>KUVVA</t>
         </is>
       </c>
       <c r="B537" s="7" t="n">
-        <v>84.59999999999999</v>
+        <v>119.6</v>
       </c>
       <c r="C537" s="8" t="n">
-        <v>-0.0018</v>
+        <v>-0.005</v>
       </c>
       <c r="D537" s="9" t="n">
-        <v>1860000</v>
+        <v>103540</v>
       </c>
       <c r="E537" s="8" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.8597</v>
       </c>
       <c r="F537" s="7" t="n">
-        <v>48.34</v>
+        <v>41.96</v>
       </c>
       <c r="G537" s="6" t="inlineStr"/>
       <c r="H537" s="7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="I537" s="8" t="n">
-        <v>-0.0331</v>
+        <v>-0.3487</v>
       </c>
       <c r="J537" s="8" t="n">
-        <v>-0.1747</v>
+        <v>-9.398999999999999</v>
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL</t>
         </is>
       </c>
       <c r="M537" s="6" t="inlineStr"/>
@@ -23856,33 +23856,33 @@
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>PRKAB</t>
+          <t>BMSTL</t>
         </is>
       </c>
       <c r="B538" s="3" t="n">
-        <v>40.58</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="C538" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0018</v>
       </c>
       <c r="D538" s="5" t="n">
-        <v>1780000</v>
+        <v>1860000</v>
       </c>
       <c r="E538" s="4" t="n">
-        <v>0.1625</v>
+        <v>0.5954999999999999</v>
       </c>
       <c r="F538" s="3" t="n">
-        <v>48.86</v>
+        <v>48.34</v>
       </c>
       <c r="G538" s="2" t="inlineStr"/>
       <c r="H538" s="3" t="n">
-        <v>9.69</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I538" s="4" t="n">
-        <v>-0.2799</v>
+        <v>-0.0331</v>
       </c>
       <c r="J538" s="4" t="n">
-        <v>0.9349</v>
+        <v>-0.1747</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="L538" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M538" s="2" t="inlineStr"/>
@@ -23899,117 +23899,117 @@
     <row r="539">
       <c r="A539" s="6" t="inlineStr">
         <is>
-          <t>GATEG</t>
+          <t>PRKAB</t>
         </is>
       </c>
       <c r="B539" s="7" t="n">
-        <v>340</v>
+        <v>40.58</v>
       </c>
       <c r="C539" s="8" t="n">
-        <v>-0.0216</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="D539" s="9" t="n">
-        <v>114090</v>
+        <v>1780000</v>
       </c>
       <c r="E539" s="8" t="n">
-        <v>0.1791</v>
+        <v>0.1625</v>
       </c>
       <c r="F539" s="7" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="G539" s="7" t="n">
-        <v>78.45</v>
-      </c>
+        <v>48.86</v>
+      </c>
+      <c r="G539" s="6" t="inlineStr"/>
       <c r="H539" s="7" t="n">
-        <v>10.12</v>
+        <v>9.69</v>
       </c>
       <c r="I539" s="8" t="n">
-        <v>0.2387</v>
-      </c>
-      <c r="J539" s="6" t="inlineStr"/>
+        <v>-0.2799</v>
+      </c>
+      <c r="J539" s="8" t="n">
+        <v>0.9349</v>
+      </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L539" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L539" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
+        </is>
+      </c>
       <c r="M539" s="6" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>ISKPL</t>
+          <t>GATEG</t>
         </is>
       </c>
       <c r="B540" s="3" t="n">
-        <v>19.4</v>
+        <v>340</v>
       </c>
       <c r="C540" s="4" t="n">
-        <v>0.007800000000000001</v>
+        <v>-0.0216</v>
       </c>
       <c r="D540" s="5" t="n">
-        <v>41020000</v>
+        <v>114090</v>
       </c>
       <c r="E540" s="4" t="n">
-        <v>0.3314</v>
+        <v>0.1791</v>
       </c>
       <c r="F540" s="3" t="n">
-        <v>78.81</v>
+        <v>56.11</v>
       </c>
       <c r="G540" s="3" t="n">
-        <v>141.81</v>
+        <v>78.45</v>
       </c>
       <c r="H540" s="3" t="n">
-        <v>10.2</v>
+        <v>10.12</v>
       </c>
       <c r="I540" s="4" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="J540" s="4" t="n">
-        <v>-0.3923</v>
-      </c>
+        <v>0.2387</v>
+      </c>
+      <c r="J540" s="2" t="inlineStr"/>
       <c r="K540" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L540" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST YILDIZ, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L540" s="2" t="inlineStr"/>
       <c r="M540" s="2" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="6" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ISKPL</t>
         </is>
       </c>
       <c r="B541" s="7" t="n">
-        <v>139.2</v>
+        <v>19.4</v>
       </c>
       <c r="C541" s="8" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="D541" s="9" t="n">
-        <v>11580000</v>
+        <v>41020000</v>
       </c>
       <c r="E541" s="8" t="n">
-        <v>0.2903</v>
+        <v>0.3314</v>
       </c>
       <c r="F541" s="7" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="G541" s="6" t="inlineStr"/>
+        <v>78.81</v>
+      </c>
+      <c r="G541" s="7" t="n">
+        <v>141.81</v>
+      </c>
       <c r="H541" s="7" t="n">
-        <v>10.44</v>
+        <v>10.2</v>
       </c>
       <c r="I541" s="8" t="n">
-        <v>0.2045</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J541" s="8" t="n">
-        <v>7.1809</v>
+        <v>-0.3923</v>
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
       </c>
       <c r="L541" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST YILDIZ, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M541" s="6" t="inlineStr"/>
@@ -24026,42 +24026,42 @@
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>LYDHO</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="B542" s="3" t="n">
-        <v>198.2</v>
+        <v>139.2</v>
       </c>
       <c r="C542" s="4" t="n">
-        <v>0.001</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D542" s="5" t="n">
-        <v>553180</v>
+        <v>11580000</v>
       </c>
       <c r="E542" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.2903</v>
       </c>
       <c r="F542" s="3" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="G542" s="3" t="n">
-        <v>156.74</v>
-      </c>
+        <v>77.48999999999999</v>
+      </c>
+      <c r="G542" s="2" t="inlineStr"/>
       <c r="H542" s="3" t="n">
-        <v>10.78</v>
+        <v>10.44</v>
       </c>
       <c r="I542" s="4" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="J542" s="2" t="inlineStr"/>
+        <v>0.2045</v>
+      </c>
+      <c r="J542" s="4" t="n">
+        <v>7.1809</v>
+      </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L542" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M542" s="2" t="inlineStr"/>
@@ -24069,42 +24069,42 @@
     <row r="543">
       <c r="A543" s="6" t="inlineStr">
         <is>
-          <t>TMPOL</t>
+          <t>LYDHO</t>
         </is>
       </c>
       <c r="B543" s="7" t="n">
-        <v>670</v>
+        <v>198.2</v>
       </c>
       <c r="C543" s="8" t="n">
-        <v>-0.0074</v>
+        <v>0.001</v>
       </c>
       <c r="D543" s="9" t="n">
-        <v>341520</v>
+        <v>553180</v>
       </c>
       <c r="E543" s="8" t="n">
-        <v>0.5454</v>
+        <v>0.2368</v>
       </c>
       <c r="F543" s="7" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="G543" s="6" t="inlineStr"/>
+        <v>57.68</v>
+      </c>
+      <c r="G543" s="7" t="n">
+        <v>156.74</v>
+      </c>
       <c r="H543" s="7" t="n">
-        <v>11.38</v>
+        <v>10.78</v>
       </c>
       <c r="I543" s="8" t="n">
-        <v>-0.0732</v>
-      </c>
-      <c r="J543" s="8" t="n">
-        <v>-0.586</v>
-      </c>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J543" s="6" t="inlineStr"/>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KAYSERİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M543" s="6" t="inlineStr"/>
@@ -24112,40 +24112,42 @@
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>TMPOL</t>
         </is>
       </c>
       <c r="B544" s="3" t="n">
-        <v>22.94</v>
+        <v>670</v>
       </c>
       <c r="C544" s="4" t="n">
-        <v>-0.0146</v>
+        <v>-0.0074</v>
       </c>
       <c r="D544" s="5" t="n">
-        <v>20820000</v>
-      </c>
-      <c r="E544" s="2" t="inlineStr"/>
+        <v>341520</v>
+      </c>
+      <c r="E544" s="4" t="n">
+        <v>0.5454</v>
+      </c>
       <c r="F544" s="3" t="n">
-        <v>49.87</v>
+        <v>70.3</v>
       </c>
       <c r="G544" s="2" t="inlineStr"/>
       <c r="H544" s="3" t="n">
-        <v>11.78</v>
+        <v>11.38</v>
       </c>
       <c r="I544" s="4" t="n">
-        <v>-0.5649000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="J544" s="4" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L544" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M544" s="2" t="inlineStr"/>
@@ -24153,44 +24155,40 @@
     <row r="545">
       <c r="A545" s="6" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="B545" s="7" t="n">
-        <v>14.4</v>
+        <v>22.94</v>
       </c>
       <c r="C545" s="8" t="n">
-        <v>-0.0028</v>
+        <v>-0.0146</v>
       </c>
       <c r="D545" s="9" t="n">
-        <v>202150000</v>
-      </c>
-      <c r="E545" s="8" t="n">
-        <v>0.9370000000000001</v>
-      </c>
+        <v>20820000</v>
+      </c>
+      <c r="E545" s="6" t="inlineStr"/>
       <c r="F545" s="7" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="G545" s="7" t="n">
-        <v>171.84</v>
-      </c>
+        <v>49.87</v>
+      </c>
+      <c r="G545" s="6" t="inlineStr"/>
       <c r="H545" s="7" t="n">
-        <v>12.06</v>
+        <v>11.78</v>
       </c>
       <c r="I545" s="8" t="n">
-        <v>0.0381</v>
+        <v>-0.5649000000000001</v>
       </c>
       <c r="J545" s="8" t="n">
-        <v>-1.5645</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
         </is>
       </c>
       <c r="M545" s="6" t="inlineStr"/>
@@ -24198,35 +24196,35 @@
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="B546" s="3" t="n">
-        <v>141.1</v>
+        <v>14.4</v>
       </c>
       <c r="C546" s="4" t="n">
-        <v>-0.0316</v>
+        <v>-0.0028</v>
       </c>
       <c r="D546" s="5" t="n">
-        <v>1590000</v>
+        <v>202150000</v>
       </c>
       <c r="E546" s="4" t="n">
-        <v>0.2463</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>63.73</v>
+        <v>57.62</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>67.27</v>
+        <v>171.84</v>
       </c>
       <c r="H546" s="3" t="n">
-        <v>12.25</v>
+        <v>12.06</v>
       </c>
       <c r="I546" s="4" t="n">
-        <v>0.2238</v>
+        <v>0.0381</v>
       </c>
       <c r="J546" s="4" t="n">
-        <v>0.1902</v>
+        <v>-1.5645</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -24235,7 +24233,7 @@
       </c>
       <c r="L546" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M546" s="2" t="inlineStr"/>
@@ -24243,42 +24241,44 @@
     <row r="547">
       <c r="A547" s="6" t="inlineStr">
         <is>
-          <t>BINBN</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B547" s="7" t="n">
-        <v>209.6</v>
+        <v>141.1</v>
       </c>
       <c r="C547" s="8" t="n">
-        <v>0.0275</v>
+        <v>-0.0316</v>
       </c>
       <c r="D547" s="9" t="n">
-        <v>1080000</v>
+        <v>1590000</v>
       </c>
       <c r="E547" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.2463</v>
       </c>
       <c r="F547" s="7" t="n">
-        <v>85.03</v>
-      </c>
-      <c r="G547" s="6" t="inlineStr"/>
+        <v>63.73</v>
+      </c>
+      <c r="G547" s="7" t="n">
+        <v>67.27</v>
+      </c>
       <c r="H547" s="7" t="n">
-        <v>12.46</v>
+        <v>12.25</v>
       </c>
       <c r="I547" s="8" t="n">
-        <v>-0.2169</v>
+        <v>0.2238</v>
       </c>
       <c r="J547" s="8" t="n">
-        <v>-0.7524</v>
+        <v>0.1902</v>
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M547" s="6" t="inlineStr"/>
@@ -24286,44 +24286,42 @@
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>BLUME</t>
+          <t>BINBN</t>
         </is>
       </c>
       <c r="B548" s="3" t="n">
-        <v>40.4</v>
+        <v>209.6</v>
       </c>
       <c r="C548" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0275</v>
       </c>
       <c r="D548" s="5" t="n">
-        <v>2460000</v>
+        <v>1080000</v>
       </c>
       <c r="E548" s="4" t="n">
-        <v>0.785</v>
+        <v>0.1071</v>
       </c>
       <c r="F548" s="3" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="G548" s="3" t="n">
-        <v>401.99</v>
-      </c>
+        <v>85.03</v>
+      </c>
+      <c r="G548" s="2" t="inlineStr"/>
       <c r="H548" s="3" t="n">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
       <c r="I548" s="4" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="J548" s="4" t="n">
-        <v>-2.1441</v>
+        <v>-0.7524</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L548" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M548" s="2" t="inlineStr"/>
@@ -24331,42 +24329,44 @@
     <row r="549">
       <c r="A549" s="6" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>BLUME</t>
         </is>
       </c>
       <c r="B549" s="7" t="n">
-        <v>60</v>
+        <v>40.4</v>
       </c>
       <c r="C549" s="8" t="n">
-        <v>-0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="D549" s="9" t="n">
-        <v>9990000</v>
+        <v>2460000</v>
       </c>
       <c r="E549" s="8" t="n">
-        <v>0.1632</v>
+        <v>0.785</v>
       </c>
       <c r="F549" s="7" t="n">
-        <v>65.16</v>
-      </c>
-      <c r="G549" s="6" t="inlineStr"/>
+        <v>33.85</v>
+      </c>
+      <c r="G549" s="7" t="n">
+        <v>401.99</v>
+      </c>
       <c r="H549" s="7" t="n">
-        <v>13.7</v>
+        <v>12.48</v>
       </c>
       <c r="I549" s="8" t="n">
-        <v>-0.1361</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="J549" s="8" t="n">
-        <v>-11.9636</v>
+        <v>-2.1441</v>
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
         </is>
       </c>
       <c r="M549" s="6" t="inlineStr"/>
@@ -24374,42 +24374,42 @@
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>SKYLP</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B550" s="3" t="n">
-        <v>369</v>
+        <v>60</v>
       </c>
       <c r="C550" s="4" t="n">
-        <v>-0.0434</v>
+        <v>-0.0025</v>
       </c>
       <c r="D550" s="5" t="n">
-        <v>160100</v>
+        <v>9990000</v>
       </c>
       <c r="E550" s="4" t="n">
-        <v>0.5749</v>
+        <v>0.1632</v>
       </c>
       <c r="F550" s="3" t="n">
-        <v>70.63</v>
+        <v>65.16</v>
       </c>
       <c r="G550" s="2" t="inlineStr"/>
       <c r="H550" s="3" t="n">
-        <v>15.32</v>
+        <v>13.7</v>
       </c>
       <c r="I550" s="4" t="n">
-        <v>-0.1301</v>
+        <v>-0.1361</v>
       </c>
       <c r="J550" s="4" t="n">
-        <v>-28.3244</v>
+        <v>-11.9636</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L550" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
         </is>
       </c>
       <c r="M550" s="2" t="inlineStr"/>
@@ -24417,78 +24417,82 @@
     <row r="551">
       <c r="A551" s="6" t="inlineStr">
         <is>
-          <t>QNBFK</t>
+          <t>SKYLP</t>
         </is>
       </c>
       <c r="B551" s="7" t="n">
-        <v>41.76</v>
+        <v>369</v>
       </c>
       <c r="C551" s="8" t="n">
-        <v>-0.0261</v>
+        <v>-0.0434</v>
       </c>
       <c r="D551" s="9" t="n">
-        <v>107190</v>
+        <v>160100</v>
       </c>
       <c r="E551" s="8" t="n">
-        <v>0.006</v>
+        <v>0.5749</v>
       </c>
       <c r="F551" s="7" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="G551" s="7" t="n">
-        <v>56.8</v>
-      </c>
+        <v>70.63</v>
+      </c>
+      <c r="G551" s="6" t="inlineStr"/>
       <c r="H551" s="7" t="n">
-        <v>16.1</v>
+        <v>15.32</v>
       </c>
       <c r="I551" s="8" t="n">
-        <v>0.3294</v>
+        <v>-0.1301</v>
       </c>
       <c r="J551" s="8" t="n">
-        <v>0.1253</v>
+        <v>-28.3244</v>
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L551" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L551" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL</t>
+        </is>
+      </c>
       <c r="M551" s="6" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>KSTUR</t>
+          <t>QNBFK</t>
         </is>
       </c>
       <c r="B552" s="3" t="n">
-        <v>3232.5</v>
+        <v>41.76</v>
       </c>
       <c r="C552" s="4" t="n">
-        <v>-0.0205</v>
+        <v>-0.0261</v>
       </c>
       <c r="D552" s="5" t="n">
-        <v>1310</v>
+        <v>107190</v>
       </c>
       <c r="E552" s="4" t="n">
-        <v>0.1952</v>
+        <v>0.006</v>
       </c>
       <c r="F552" s="3" t="n">
-        <v>50.66</v>
+        <v>44.45</v>
       </c>
       <c r="G552" s="3" t="n">
-        <v>162.76</v>
+        <v>56.8</v>
       </c>
       <c r="H552" s="3" t="n">
-        <v>16.16</v>
+        <v>16.1</v>
       </c>
       <c r="I552" s="4" t="n">
-        <v>0.1129</v>
-      </c>
-      <c r="J552" s="2" t="inlineStr"/>
+        <v>0.3294</v>
+      </c>
+      <c r="J552" s="4" t="n">
+        <v>0.1253</v>
+      </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L552" s="2" t="inlineStr"/>
@@ -24497,89 +24501,83 @@
     <row r="553">
       <c r="A553" s="6" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>KSTUR</t>
         </is>
       </c>
       <c r="B553" s="7" t="n">
-        <v>285</v>
+        <v>3232.5</v>
       </c>
       <c r="C553" s="8" t="n">
-        <v>-0.0044</v>
+        <v>-0.0205</v>
       </c>
       <c r="D553" s="9" t="n">
-        <v>807110</v>
+        <v>1310</v>
       </c>
       <c r="E553" s="8" t="n">
-        <v>0.3512</v>
+        <v>0.1952</v>
       </c>
       <c r="F553" s="7" t="n">
-        <v>61.7</v>
+        <v>50.66</v>
       </c>
       <c r="G553" s="7" t="n">
-        <v>137.79</v>
+        <v>162.76</v>
       </c>
       <c r="H553" s="7" t="n">
-        <v>16.7</v>
+        <v>16.16</v>
       </c>
       <c r="I553" s="8" t="n">
-        <v>0.1448</v>
-      </c>
-      <c r="J553" s="8" t="n">
-        <v>0.4836</v>
-      </c>
+        <v>0.1129</v>
+      </c>
+      <c r="J553" s="6" t="inlineStr"/>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
-        </is>
-      </c>
-      <c r="L553" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST ANKARA</t>
-        </is>
-      </c>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
+      <c r="L553" s="6" t="inlineStr"/>
       <c r="M553" s="6" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B554" s="3" t="n">
-        <v>326.5</v>
+        <v>285</v>
       </c>
       <c r="C554" s="4" t="n">
-        <v>0.0046</v>
+        <v>-0.0044</v>
       </c>
       <c r="D554" s="5" t="n">
-        <v>2860000</v>
+        <v>807110</v>
       </c>
       <c r="E554" s="4" t="n">
-        <v>0.3721</v>
+        <v>0.3512</v>
       </c>
       <c r="F554" s="3" t="n">
-        <v>79.44</v>
+        <v>61.7</v>
       </c>
       <c r="G554" s="3" t="n">
-        <v>46.81</v>
+        <v>137.79</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>17.39</v>
+        <v>16.7</v>
       </c>
       <c r="I554" s="4" t="n">
-        <v>0.4916</v>
+        <v>0.1448</v>
       </c>
       <c r="J554" s="4" t="n">
-        <v>2.6125</v>
+        <v>0.4836</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L554" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M554" s="2" t="inlineStr"/>
@@ -24587,122 +24585,124 @@
     <row r="555">
       <c r="A555" s="6" t="inlineStr">
         <is>
-          <t>DIRIT</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B555" s="7" t="n">
-        <v>29</v>
+        <v>326.5</v>
       </c>
       <c r="C555" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0046</v>
       </c>
       <c r="D555" s="9" t="n">
-        <v>66260</v>
-      </c>
-      <c r="E555" s="6" t="inlineStr"/>
+        <v>2860000</v>
+      </c>
+      <c r="E555" s="8" t="n">
+        <v>0.3721</v>
+      </c>
       <c r="F555" s="7" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="G555" s="6" t="inlineStr"/>
+        <v>79.44</v>
+      </c>
+      <c r="G555" s="7" t="n">
+        <v>46.81</v>
+      </c>
       <c r="H555" s="7" t="n">
-        <v>17.95</v>
+        <v>17.39</v>
       </c>
       <c r="I555" s="8" t="n">
-        <v>-2.156</v>
+        <v>0.4916</v>
       </c>
       <c r="J555" s="8" t="n">
-        <v>-67.1895</v>
+        <v>2.6125</v>
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L555" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L555" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
+        </is>
+      </c>
       <c r="M555" s="6" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>VKING</t>
+          <t>DIRIT</t>
         </is>
       </c>
       <c r="B556" s="3" t="n">
-        <v>26.82</v>
+        <v>29</v>
       </c>
       <c r="C556" s="4" t="n">
-        <v>-0.0176</v>
+        <v>0.0284</v>
       </c>
       <c r="D556" s="5" t="n">
-        <v>910870</v>
-      </c>
-      <c r="E556" s="4" t="n">
-        <v>0.9698</v>
-      </c>
+        <v>66260</v>
+      </c>
+      <c r="E556" s="2" t="inlineStr"/>
       <c r="F556" s="3" t="n">
-        <v>50.55</v>
+        <v>54.76</v>
       </c>
       <c r="G556" s="2" t="inlineStr"/>
       <c r="H556" s="3" t="n">
-        <v>18.73</v>
+        <v>17.95</v>
       </c>
       <c r="I556" s="4" t="n">
-        <v>-19.6981</v>
+        <v>-2.156</v>
       </c>
       <c r="J556" s="4" t="n">
-        <v>-0.7162999999999999</v>
+        <v>-67.1895</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L556" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L556" s="2" t="inlineStr"/>
       <c r="M556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="6" t="inlineStr">
         <is>
-          <t>COSMO</t>
+          <t>VKING</t>
         </is>
       </c>
       <c r="B557" s="7" t="n">
-        <v>206.9</v>
+        <v>26.82</v>
       </c>
       <c r="C557" s="8" t="n">
-        <v>-0.01</v>
+        <v>-0.0176</v>
       </c>
       <c r="D557" s="9" t="n">
-        <v>70020</v>
+        <v>910870</v>
       </c>
       <c r="E557" s="8" t="n">
-        <v>0.5483</v>
+        <v>0.9698</v>
       </c>
       <c r="F557" s="7" t="n">
-        <v>47.04</v>
+        <v>50.55</v>
       </c>
       <c r="G557" s="6" t="inlineStr"/>
       <c r="H557" s="7" t="n">
-        <v>18.8</v>
+        <v>18.73</v>
       </c>
       <c r="I557" s="8" t="n">
-        <v>-0.1124</v>
+        <v>-19.6981</v>
       </c>
       <c r="J557" s="8" t="n">
-        <v>-1.529</v>
+        <v>-0.7162999999999999</v>
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M557" s="6" t="inlineStr"/>
@@ -24710,44 +24710,42 @@
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>COSMO</t>
         </is>
       </c>
       <c r="B558" s="3" t="n">
-        <v>103.6</v>
+        <v>206.9</v>
       </c>
       <c r="C558" s="4" t="n">
-        <v>0.036</v>
+        <v>-0.01</v>
       </c>
       <c r="D558" s="5" t="n">
-        <v>40600000</v>
+        <v>70020</v>
       </c>
       <c r="E558" s="4" t="n">
-        <v>0.2784</v>
+        <v>0.5483</v>
       </c>
       <c r="F558" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="G558" s="3" t="n">
-        <v>24.88</v>
-      </c>
+        <v>47.04</v>
+      </c>
+      <c r="G558" s="2" t="inlineStr"/>
       <c r="H558" s="3" t="n">
-        <v>18.84</v>
+        <v>18.8</v>
       </c>
       <c r="I558" s="4" t="n">
-        <v>1.1992</v>
+        <v>-0.1124</v>
       </c>
       <c r="J558" s="4" t="n">
-        <v>0.3524</v>
+        <v>-1.529</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L558" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M558" s="2" t="inlineStr"/>
@@ -24755,42 +24753,44 @@
     <row r="559">
       <c r="A559" s="6" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B559" s="7" t="n">
-        <v>446.75</v>
+        <v>103.6</v>
       </c>
       <c r="C559" s="8" t="n">
-        <v>-0.0067</v>
+        <v>0.036</v>
       </c>
       <c r="D559" s="9" t="n">
-        <v>1910000</v>
+        <v>40600000</v>
       </c>
       <c r="E559" s="8" t="n">
-        <v>0.3221</v>
+        <v>0.2784</v>
       </c>
       <c r="F559" s="7" t="n">
-        <v>84.39</v>
-      </c>
-      <c r="G559" s="6" t="inlineStr"/>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G559" s="7" t="n">
+        <v>24.88</v>
+      </c>
       <c r="H559" s="7" t="n">
-        <v>18.88</v>
+        <v>18.84</v>
       </c>
       <c r="I559" s="8" t="n">
-        <v>-0.0564</v>
+        <v>1.1992</v>
       </c>
       <c r="J559" s="8" t="n">
-        <v>-6790.5101</v>
+        <v>0.3524</v>
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M559" s="6" t="inlineStr"/>
@@ -24798,40 +24798,42 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>VKFYO</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="B560" s="3" t="n">
-        <v>35.32</v>
+        <v>446.75</v>
       </c>
       <c r="C560" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0067</v>
       </c>
       <c r="D560" s="5" t="n">
-        <v>421350</v>
-      </c>
-      <c r="E560" s="2" t="inlineStr"/>
+        <v>1910000</v>
+      </c>
+      <c r="E560" s="4" t="n">
+        <v>0.3221</v>
+      </c>
       <c r="F560" s="3" t="n">
-        <v>56.57</v>
+        <v>84.39</v>
       </c>
       <c r="G560" s="2" t="inlineStr"/>
       <c r="H560" s="3" t="n">
-        <v>19.15</v>
+        <v>18.88</v>
       </c>
       <c r="I560" s="4" t="n">
-        <v>-0.3087</v>
+        <v>-0.0564</v>
       </c>
       <c r="J560" s="4" t="n">
-        <v>0.4908</v>
+        <v>-6790.5101</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L560" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M560" s="2" t="inlineStr"/>
@@ -24839,42 +24841,40 @@
     <row r="561">
       <c r="A561" s="6" t="inlineStr">
         <is>
-          <t>MRSHL</t>
-        </is>
-      </c>
-      <c r="B561" s="9" t="n">
-        <v>1578</v>
+          <t>VKFYO</t>
+        </is>
+      </c>
+      <c r="B561" s="7" t="n">
+        <v>35.32</v>
       </c>
       <c r="C561" s="8" t="n">
-        <v>0.0019</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D561" s="9" t="n">
-        <v>45470</v>
-      </c>
-      <c r="E561" s="8" t="n">
-        <v>0.0639</v>
-      </c>
+        <v>421350</v>
+      </c>
+      <c r="E561" s="6" t="inlineStr"/>
       <c r="F561" s="7" t="n">
-        <v>64.23999999999999</v>
+        <v>56.57</v>
       </c>
       <c r="G561" s="6" t="inlineStr"/>
       <c r="H561" s="7" t="n">
-        <v>19.73</v>
+        <v>19.15</v>
       </c>
       <c r="I561" s="8" t="n">
-        <v>-0.3366</v>
+        <v>-0.3087</v>
       </c>
       <c r="J561" s="8" t="n">
-        <v>0.5811999999999999</v>
+        <v>0.4908</v>
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M561" s="6" t="inlineStr"/>
@@ -24882,126 +24882,124 @@
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>KENT</t>
-        </is>
-      </c>
-      <c r="B562" s="3" t="n">
-        <v>421.25</v>
+          <t>MRSHL</t>
+        </is>
+      </c>
+      <c r="B562" s="5" t="n">
+        <v>1578</v>
       </c>
       <c r="C562" s="4" t="n">
-        <v>-0.0198</v>
+        <v>0.0019</v>
       </c>
       <c r="D562" s="5" t="n">
-        <v>6450</v>
+        <v>45470</v>
       </c>
       <c r="E562" s="4" t="n">
-        <v>0.0059</v>
+        <v>0.0639</v>
       </c>
       <c r="F562" s="3" t="n">
-        <v>45.25</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="G562" s="2" t="inlineStr"/>
       <c r="H562" s="3" t="n">
-        <v>20.39</v>
+        <v>19.73</v>
       </c>
       <c r="I562" s="4" t="n">
-        <v>-0.0998</v>
+        <v>-0.3366</v>
       </c>
       <c r="J562" s="4" t="n">
-        <v>-4.3494</v>
+        <v>0.5811999999999999</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L562" s="2" t="inlineStr"/>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L562" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="6" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="B563" s="7" t="n">
-        <v>98.05</v>
+        <v>421.25</v>
       </c>
       <c r="C563" s="8" t="n">
-        <v>0</v>
+        <v>-0.0198</v>
       </c>
       <c r="D563" s="9" t="n">
-        <v>9470000</v>
+        <v>6450</v>
       </c>
       <c r="E563" s="8" t="n">
-        <v>0.3576</v>
+        <v>0.0059</v>
       </c>
       <c r="F563" s="7" t="n">
-        <v>91.48999999999999</v>
+        <v>45.25</v>
       </c>
       <c r="G563" s="6" t="inlineStr"/>
       <c r="H563" s="7" t="n">
-        <v>23.48</v>
+        <v>20.39</v>
       </c>
       <c r="I563" s="8" t="n">
-        <v>-0.2916</v>
+        <v>-0.0998</v>
       </c>
       <c r="J563" s="8" t="n">
-        <v>-0.6609</v>
+        <v>-4.3494</v>
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L563" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, STOXX Emerging Markets 1500</t>
-        </is>
-      </c>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
+      <c r="L563" s="6" t="inlineStr"/>
       <c r="M563" s="6" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>PASEU</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="B564" s="3" t="n">
-        <v>124.9</v>
+        <v>98.05</v>
       </c>
       <c r="C564" s="4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="D564" s="5" t="n">
-        <v>5150000</v>
+        <v>9470000</v>
       </c>
       <c r="E564" s="4" t="n">
-        <v>0.3205</v>
+        <v>0.3576</v>
       </c>
       <c r="F564" s="3" t="n">
-        <v>54.57</v>
-      </c>
-      <c r="G564" s="3" t="n">
-        <v>76.95</v>
-      </c>
+        <v>91.48999999999999</v>
+      </c>
+      <c r="G564" s="2" t="inlineStr"/>
       <c r="H564" s="3" t="n">
-        <v>23.92</v>
+        <v>23.48</v>
       </c>
       <c r="I564" s="4" t="n">
-        <v>0.4103</v>
+        <v>-0.2916</v>
       </c>
       <c r="J564" s="4" t="n">
-        <v>30.5521</v>
+        <v>-0.6609</v>
       </c>
       <c r="K564" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L564" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M564" s="2" t="inlineStr"/>
@@ -25009,42 +25007,44 @@
     <row r="565">
       <c r="A565" s="6" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>PASEU</t>
         </is>
       </c>
       <c r="B565" s="7" t="n">
-        <v>94.2</v>
+        <v>124.9</v>
       </c>
       <c r="C565" s="8" t="n">
-        <v>0.0284</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D565" s="9" t="n">
-        <v>10660000</v>
+        <v>5150000</v>
       </c>
       <c r="E565" s="8" t="n">
-        <v>0.948</v>
+        <v>0.3205</v>
       </c>
       <c r="F565" s="7" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="G565" s="6" t="inlineStr"/>
+        <v>54.57</v>
+      </c>
+      <c r="G565" s="7" t="n">
+        <v>76.95</v>
+      </c>
       <c r="H565" s="7" t="n">
-        <v>26.27</v>
+        <v>23.92</v>
       </c>
       <c r="I565" s="8" t="n">
-        <v>-0.7977</v>
+        <v>0.4103</v>
       </c>
       <c r="J565" s="8" t="n">
-        <v>-4.018899999999999</v>
+        <v>30.5521</v>
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M565" s="6" t="inlineStr"/>
@@ -25052,40 +25052,42 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>IZFAS</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B566" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="C566" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0284</v>
       </c>
       <c r="D566" s="5" t="n">
-        <v>9740000</v>
+        <v>10660000</v>
       </c>
       <c r="E566" s="4" t="n">
-        <v>0.9309000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="F566" s="3" t="n">
-        <v>72.20999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="G566" s="2" t="inlineStr"/>
       <c r="H566" s="3" t="n">
-        <v>30.54</v>
+        <v>26.27</v>
       </c>
       <c r="I566" s="4" t="n">
-        <v>-0.1302</v>
-      </c>
-      <c r="J566" s="2" t="inlineStr"/>
+        <v>-0.7977</v>
+      </c>
+      <c r="J566" s="4" t="n">
+        <v>-4.018899999999999</v>
+      </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L566" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST İZMİR</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M566" s="2" t="inlineStr"/>
@@ -25093,42 +25095,40 @@
     <row r="567">
       <c r="A567" s="6" t="inlineStr">
         <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="B567" s="9" t="n">
-        <v>1629</v>
+          <t>IZFAS</t>
+        </is>
+      </c>
+      <c r="B567" s="7" t="n">
+        <v>68.90000000000001</v>
       </c>
       <c r="C567" s="8" t="n">
-        <v>0.0181</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D567" s="9" t="n">
-        <v>26470</v>
+        <v>9740000</v>
       </c>
       <c r="E567" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.9309000000000001</v>
       </c>
       <c r="F567" s="7" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="G567" s="7" t="n">
-        <v>158.89</v>
-      </c>
+        <v>72.20999999999999</v>
+      </c>
+      <c r="G567" s="6" t="inlineStr"/>
       <c r="H567" s="7" t="n">
-        <v>31.13</v>
+        <v>30.54</v>
       </c>
       <c r="I567" s="8" t="n">
-        <v>0.2442</v>
+        <v>-0.1302</v>
       </c>
       <c r="J567" s="6" t="inlineStr"/>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST İZMİR</t>
         </is>
       </c>
       <c r="M567" s="6" t="inlineStr"/>
@@ -25136,44 +25136,42 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>BFREN</t>
-        </is>
-      </c>
-      <c r="B568" s="3" t="n">
-        <v>150.5</v>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="B568" s="5" t="n">
+        <v>1629</v>
       </c>
       <c r="C568" s="4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0181</v>
       </c>
       <c r="D568" s="5" t="n">
-        <v>687340</v>
+        <v>26470</v>
       </c>
       <c r="E568" s="4" t="n">
-        <v>0.1549</v>
+        <v>0.3704</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>55.93</v>
+        <v>53.15</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>168.21</v>
+        <v>158.89</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>32.04</v>
+        <v>31.13</v>
       </c>
       <c r="I568" s="4" t="n">
-        <v>0.2511</v>
-      </c>
-      <c r="J568" s="4" t="n">
-        <v>-0.2499</v>
-      </c>
+        <v>0.2442</v>
+      </c>
+      <c r="J568" s="2" t="inlineStr"/>
       <c r="K568" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L568" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M568" s="2" t="inlineStr"/>
@@ -25181,40 +25179,44 @@
     <row r="569">
       <c r="A569" s="6" t="inlineStr">
         <is>
-          <t>IHAAS</t>
+          <t>BFREN</t>
         </is>
       </c>
       <c r="B569" s="7" t="n">
-        <v>78</v>
+        <v>150.5</v>
       </c>
       <c r="C569" s="8" t="n">
-        <v>-0.017</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D569" s="9" t="n">
-        <v>2040000</v>
+        <v>687340</v>
       </c>
       <c r="E569" s="8" t="n">
-        <v>0.3438000000000001</v>
+        <v>0.1549</v>
       </c>
       <c r="F569" s="7" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="G569" s="6" t="inlineStr"/>
+        <v>55.93</v>
+      </c>
+      <c r="G569" s="7" t="n">
+        <v>168.21</v>
+      </c>
       <c r="H569" s="7" t="n">
-        <v>37.47</v>
+        <v>32.04</v>
       </c>
       <c r="I569" s="8" t="n">
-        <v>-0.2336</v>
-      </c>
-      <c r="J569" s="6" t="inlineStr"/>
+        <v>0.2511</v>
+      </c>
+      <c r="J569" s="8" t="n">
+        <v>-0.2499</v>
+      </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST BURSA</t>
         </is>
       </c>
       <c r="M569" s="6" t="inlineStr"/>
@@ -25222,42 +25224,40 @@
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>IHAAS</t>
         </is>
       </c>
       <c r="B570" s="3" t="n">
-        <v>875</v>
+        <v>78</v>
       </c>
       <c r="C570" s="4" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="D570" s="5" t="n">
-        <v>464140</v>
+        <v>2040000</v>
       </c>
       <c r="E570" s="4" t="n">
-        <v>0.2188</v>
+        <v>0.3438000000000001</v>
       </c>
       <c r="F570" s="3" t="n">
-        <v>62.02</v>
+        <v>49.11</v>
       </c>
       <c r="G570" s="2" t="inlineStr"/>
       <c r="H570" s="3" t="n">
-        <v>43.41</v>
+        <v>37.47</v>
       </c>
       <c r="I570" s="4" t="n">
-        <v>-0.1359</v>
-      </c>
-      <c r="J570" s="4" t="n">
-        <v>-0.6534</v>
-      </c>
+        <v>-0.2336</v>
+      </c>
+      <c r="J570" s="2" t="inlineStr"/>
       <c r="K570" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L570" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M570" s="2" t="inlineStr"/>
@@ -25265,44 +25265,42 @@
     <row r="571">
       <c r="A571" s="6" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="B571" s="7" t="n">
-        <v>131.5</v>
+        <v>875</v>
       </c>
       <c r="C571" s="8" t="n">
-        <v>0.0077</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="D571" s="9" t="n">
-        <v>2630000</v>
+        <v>464140</v>
       </c>
       <c r="E571" s="8" t="n">
-        <v>0.2306</v>
+        <v>0.2188</v>
       </c>
       <c r="F571" s="7" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="G571" s="7" t="n">
-        <v>161.43</v>
-      </c>
+        <v>62.02</v>
+      </c>
+      <c r="G571" s="6" t="inlineStr"/>
       <c r="H571" s="7" t="n">
-        <v>44.5</v>
+        <v>43.41</v>
       </c>
       <c r="I571" s="8" t="n">
-        <v>0.3759</v>
+        <v>-0.1359</v>
       </c>
       <c r="J571" s="8" t="n">
-        <v>0.9841</v>
+        <v>-0.6534</v>
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA, STOXX Emerging Markets 1500</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M571" s="6" t="inlineStr"/>
@@ -25310,122 +25308,124 @@
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>BALAT</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="B572" s="3" t="n">
-        <v>84.45</v>
+        <v>131.5</v>
       </c>
       <c r="C572" s="4" t="n">
-        <v>-0.018</v>
+        <v>0.0077</v>
       </c>
       <c r="D572" s="5" t="n">
-        <v>57780</v>
+        <v>2630000</v>
       </c>
       <c r="E572" s="4" t="n">
-        <v>0.8389</v>
+        <v>0.2306</v>
       </c>
       <c r="F572" s="3" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="G572" s="2" t="inlineStr"/>
+        <v>52.6</v>
+      </c>
+      <c r="G572" s="3" t="n">
+        <v>161.43</v>
+      </c>
       <c r="H572" s="3" t="n">
-        <v>44.77</v>
+        <v>44.5</v>
       </c>
       <c r="I572" s="4" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="J572" s="2" t="inlineStr"/>
+        <v>0.3759</v>
+      </c>
+      <c r="J572" s="4" t="n">
+        <v>0.9841</v>
+      </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L572" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L572" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA, STOXX Emerging Markets 1500</t>
+        </is>
+      </c>
       <c r="M572" s="2" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="6" t="inlineStr">
         <is>
-          <t>ODINE</t>
+          <t>BALAT</t>
         </is>
       </c>
       <c r="B573" s="7" t="n">
-        <v>975</v>
+        <v>84.45</v>
       </c>
       <c r="C573" s="8" t="n">
-        <v>0.0372</v>
+        <v>-0.018</v>
       </c>
       <c r="D573" s="9" t="n">
-        <v>450400</v>
+        <v>57780</v>
       </c>
       <c r="E573" s="8" t="n">
-        <v>0.0535</v>
+        <v>0.8389</v>
       </c>
       <c r="F573" s="7" t="n">
-        <v>79.52</v>
-      </c>
-      <c r="G573" s="7" t="n">
-        <v>300.45</v>
-      </c>
+        <v>37.15</v>
+      </c>
+      <c r="G573" s="6" t="inlineStr"/>
       <c r="H573" s="7" t="n">
-        <v>52.54</v>
+        <v>44.77</v>
       </c>
       <c r="I573" s="8" t="n">
-        <v>0.2047</v>
+        <v>-0.4094</v>
       </c>
       <c r="J573" s="6" t="inlineStr"/>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L573" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L573" s="6" t="inlineStr"/>
       <c r="M573" s="6" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>POLTK</t>
-        </is>
-      </c>
-      <c r="B574" s="5" t="n">
-        <v>5600</v>
+          <t>ODINE</t>
+        </is>
+      </c>
+      <c r="B574" s="3" t="n">
+        <v>975</v>
       </c>
       <c r="C574" s="4" t="n">
-        <v>-0.015</v>
+        <v>0.0372</v>
       </c>
       <c r="D574" s="5" t="n">
-        <v>19300</v>
+        <v>450400</v>
       </c>
       <c r="E574" s="4" t="n">
-        <v>0.1973</v>
+        <v>0.0535</v>
       </c>
       <c r="F574" s="3" t="n">
-        <v>54.63</v>
-      </c>
-      <c r="G574" s="2" t="inlineStr"/>
+        <v>79.52</v>
+      </c>
+      <c r="G574" s="3" t="n">
+        <v>300.45</v>
+      </c>
       <c r="H574" s="3" t="n">
-        <v>66.58</v>
+        <v>52.54</v>
       </c>
       <c r="I574" s="4" t="n">
-        <v>-0.1117</v>
-      </c>
-      <c r="J574" s="4" t="n">
-        <v>-5.8214</v>
-      </c>
+        <v>0.2047</v>
+      </c>
+      <c r="J574" s="2" t="inlineStr"/>
       <c r="K574" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L574" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST KOBİ SANAYİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M574" s="2" t="inlineStr"/>
@@ -25433,44 +25433,42 @@
     <row r="575">
       <c r="A575" s="6" t="inlineStr">
         <is>
-          <t>DSTKF</t>
+          <t>POLTK</t>
         </is>
       </c>
       <c r="B575" s="9" t="n">
-        <v>2525</v>
+        <v>5600</v>
       </c>
       <c r="C575" s="8" t="n">
-        <v>0.0421</v>
+        <v>-0.015</v>
       </c>
       <c r="D575" s="9" t="n">
-        <v>636780</v>
+        <v>19300</v>
       </c>
       <c r="E575" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1973</v>
       </c>
       <c r="F575" s="7" t="n">
-        <v>92.55</v>
-      </c>
-      <c r="G575" s="7" t="n">
-        <v>223.5</v>
-      </c>
+        <v>54.63</v>
+      </c>
+      <c r="G575" s="6" t="inlineStr"/>
       <c r="H575" s="7" t="n">
-        <v>68.95</v>
+        <v>66.58</v>
       </c>
       <c r="I575" s="8" t="n">
-        <v>0.4482</v>
+        <v>-0.1117</v>
       </c>
       <c r="J575" s="8" t="n">
-        <v>0.09619999999999999</v>
+        <v>-5.8214</v>
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HALKA ARZ, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST KOBİ SANAYİ</t>
         </is>
       </c>
       <c r="M575" s="6" t="inlineStr"/>
@@ -25478,44 +25476,44 @@
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>PKENT</t>
-        </is>
-      </c>
-      <c r="B576" s="3" t="n">
-        <v>162.1</v>
+          <t>DSTKF</t>
+        </is>
+      </c>
+      <c r="B576" s="5" t="n">
+        <v>2525</v>
       </c>
       <c r="C576" s="4" t="n">
-        <v>-0.0134</v>
+        <v>0.0421</v>
       </c>
       <c r="D576" s="5" t="n">
-        <v>630720</v>
+        <v>636780</v>
       </c>
       <c r="E576" s="4" t="n">
-        <v>0.3278</v>
+        <v>0.25</v>
       </c>
       <c r="F576" s="3" t="n">
-        <v>51.8</v>
+        <v>92.55</v>
       </c>
       <c r="G576" s="3" t="n">
-        <v>753.25</v>
+        <v>223.5</v>
       </c>
       <c r="H576" s="3" t="n">
-        <v>75.05</v>
+        <v>68.95</v>
       </c>
       <c r="I576" s="4" t="n">
-        <v>0.1167</v>
+        <v>0.4482</v>
       </c>
       <c r="J576" s="4" t="n">
-        <v>-0.9891</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L576" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HALKA ARZ, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M576" s="2" t="inlineStr"/>
@@ -25523,40 +25521,44 @@
     <row r="577">
       <c r="A577" s="6" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>PKENT</t>
         </is>
       </c>
       <c r="B577" s="7" t="n">
-        <v>117.7</v>
+        <v>162.1</v>
       </c>
       <c r="C577" s="8" t="n">
-        <v>0.0848</v>
+        <v>-0.0134</v>
       </c>
       <c r="D577" s="9" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="E577" s="6" t="inlineStr"/>
+        <v>630720</v>
+      </c>
+      <c r="E577" s="8" t="n">
+        <v>0.3278</v>
+      </c>
       <c r="F577" s="7" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="G577" s="6" t="inlineStr"/>
+        <v>51.8</v>
+      </c>
+      <c r="G577" s="7" t="n">
+        <v>753.25</v>
+      </c>
       <c r="H577" s="7" t="n">
-        <v>76.87</v>
+        <v>75.05</v>
       </c>
       <c r="I577" s="8" t="n">
-        <v>-0.6681</v>
+        <v>0.1167</v>
       </c>
       <c r="J577" s="8" t="n">
-        <v>-0.3896</v>
+        <v>-0.9891</v>
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
         </is>
       </c>
       <c r="M577" s="6" t="inlineStr"/>
@@ -25564,44 +25566,40 @@
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>ISBTR</t>
-        </is>
-      </c>
-      <c r="B578" s="5" t="n">
-        <v>415000</v>
+          <t>DOGUB</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="n">
+        <v>117.7</v>
       </c>
       <c r="C578" s="4" t="n">
-        <v>-0.0393</v>
-      </c>
-      <c r="D578" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E578" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.0848</v>
+      </c>
+      <c r="D578" s="5" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="E578" s="2" t="inlineStr"/>
       <c r="F578" s="3" t="n">
-        <v>42.36</v>
-      </c>
-      <c r="G578" s="3" t="n">
-        <v>540.13</v>
-      </c>
+        <v>61.46</v>
+      </c>
+      <c r="G578" s="2" t="inlineStr"/>
       <c r="H578" s="3" t="n">
-        <v>85.64</v>
+        <v>76.87</v>
       </c>
       <c r="I578" s="4" t="n">
-        <v>0.1819</v>
+        <v>-0.6681</v>
       </c>
       <c r="J578" s="4" t="n">
-        <v>0.6855</v>
+        <v>-0.3896</v>
       </c>
       <c r="K578" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L578" s="2" t="inlineStr">
         <is>
-          <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
         </is>
       </c>
       <c r="M578" s="2" t="inlineStr"/>
@@ -25609,42 +25607,44 @@
     <row r="579">
       <c r="A579" s="6" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="B579" s="9" t="n">
-        <v>1054</v>
+        <v>415000</v>
       </c>
       <c r="C579" s="8" t="n">
-        <v>-0.0286</v>
-      </c>
-      <c r="D579" s="9" t="n">
-        <v>85530</v>
+        <v>-0.0393</v>
+      </c>
+      <c r="D579" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E579" s="8" t="n">
-        <v>0.5552</v>
+        <v>1</v>
       </c>
       <c r="F579" s="7" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="G579" s="6" t="inlineStr"/>
+        <v>42.36</v>
+      </c>
+      <c r="G579" s="7" t="n">
+        <v>540.13</v>
+      </c>
       <c r="H579" s="7" t="n">
-        <v>91.94</v>
+        <v>85.64</v>
       </c>
       <c r="I579" s="8" t="n">
-        <v>-0.4695</v>
+        <v>0.1819</v>
       </c>
       <c r="J579" s="8" t="n">
-        <v>0.4335</v>
+        <v>0.6855</v>
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST BURSA</t>
+          <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
         </is>
       </c>
       <c r="M579" s="6" t="inlineStr"/>
@@ -25652,33 +25652,33 @@
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>ULUSE</t>
-        </is>
-      </c>
-      <c r="B580" s="3" t="n">
-        <v>250.25</v>
+          <t>BURVA</t>
+        </is>
+      </c>
+      <c r="B580" s="5" t="n">
+        <v>1054</v>
       </c>
       <c r="C580" s="4" t="n">
-        <v>-0.001</v>
+        <v>-0.0286</v>
       </c>
       <c r="D580" s="5" t="n">
-        <v>691130</v>
+        <v>85530</v>
       </c>
       <c r="E580" s="4" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.5552</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>78.31999999999999</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="G580" s="2" t="inlineStr"/>
       <c r="H580" s="3" t="n">
-        <v>139.18</v>
+        <v>91.94</v>
       </c>
       <c r="I580" s="4" t="n">
-        <v>-0.9847</v>
+        <v>-0.4695</v>
       </c>
       <c r="J580" s="4" t="n">
-        <v>-2.8801</v>
+        <v>0.4335</v>
       </c>
       <c r="K580" s="2" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="L580" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST BURSA</t>
         </is>
       </c>
       <c r="M580" s="2" t="inlineStr"/>
@@ -25695,44 +25695,42 @@
     <row r="581">
       <c r="A581" s="6" t="inlineStr">
         <is>
-          <t>TRHOL</t>
-        </is>
-      </c>
-      <c r="B581" s="9" t="n">
-        <v>1321</v>
+          <t>ULUSE</t>
+        </is>
+      </c>
+      <c r="B581" s="7" t="n">
+        <v>250.25</v>
       </c>
       <c r="C581" s="8" t="n">
-        <v>0.0123</v>
+        <v>-0.001</v>
       </c>
       <c r="D581" s="9" t="n">
-        <v>212650</v>
+        <v>691130</v>
       </c>
       <c r="E581" s="8" t="n">
-        <v>0.9958</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F581" s="7" t="n">
-        <v>77.86</v>
-      </c>
-      <c r="G581" s="7" t="n">
-        <v>460.31</v>
-      </c>
+        <v>78.31999999999999</v>
+      </c>
+      <c r="G581" s="6" t="inlineStr"/>
       <c r="H581" s="7" t="n">
-        <v>251.34</v>
+        <v>139.18</v>
       </c>
       <c r="I581" s="8" t="n">
-        <v>0.8465</v>
+        <v>-0.9847</v>
       </c>
       <c r="J581" s="8" t="n">
-        <v>-0.7746999999999999</v>
+        <v>-2.8801</v>
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M581" s="6" t="inlineStr"/>
@@ -25740,67 +25738,81 @@
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
-        <v>2749985</v>
+        <v>1321</v>
       </c>
       <c r="C582" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D582" s="3" t="n">
-        <v>1</v>
+        <v>0.0123</v>
+      </c>
+      <c r="D582" s="5" t="n">
+        <v>212650</v>
       </c>
       <c r="E582" s="4" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="F582" s="3" t="n">
-        <v>44.27</v>
+        <v>77.86</v>
       </c>
       <c r="G582" s="3" t="n">
-        <v>1012923.13</v>
+        <v>460.31</v>
       </c>
       <c r="H582" s="3" t="n">
-        <v>160607.07</v>
+        <v>251.34</v>
       </c>
       <c r="I582" s="4" t="n">
-        <v>0.1819</v>
+        <v>0.8465</v>
       </c>
       <c r="J582" s="4" t="n">
-        <v>0.6855</v>
+        <v>-0.7746999999999999</v>
       </c>
       <c r="K582" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
         </is>
       </c>
-      <c r="L582" s="2" t="inlineStr"/>
+      <c r="L582" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
+        </is>
+      </c>
       <c r="M582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
-        </is>
-      </c>
-      <c r="B583" s="7" t="n">
-        <v>6.13</v>
+          <t>ISKUR</t>
+        </is>
+      </c>
+      <c r="B583" s="9" t="n">
+        <v>2749985</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="D583" s="9" t="n">
-        <v>8730000</v>
-      </c>
-      <c r="E583" s="6" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="D583" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E583" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F583" s="7" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="G583" s="6" t="inlineStr"/>
-      <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
+        <v>44.27</v>
+      </c>
+      <c r="G583" s="7" t="n">
+        <v>1012923.13</v>
+      </c>
+      <c r="H583" s="7" t="n">
+        <v>160607.07</v>
+      </c>
+      <c r="I583" s="8" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="J583" s="8" t="n">
+        <v>0.6855</v>
+      </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -25812,21 +25824,21 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>2.82</v>
+        <v>197.4</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.099</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>263430000</v>
+        <v>20610000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>52.07</v>
+        <v>45.87</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25834,12 +25846,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25847,38 +25859,34 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>10.56</v>
+        <v>24.62</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>255670000</v>
-      </c>
-      <c r="E585" s="8" t="n">
-        <v>0.2479</v>
-      </c>
+        <v>15600000</v>
+      </c>
+      <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>53.86</v>
+        <v>56.05</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="8" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
+      <c r="I585" s="6" t="inlineStr"/>
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25886,23 +25894,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>251</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0595</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E586" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>14880000</v>
+      </c>
+      <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>46.72</v>
+        <v>61.35</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25910,30 +25916,34 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>41.38</v>
+        <v>39.64</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0222</v>
+        <v>0.0195</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>10990000</v>
+        <v>12770000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>60.95</v>
+        <v>52.02</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25941,12 +25951,12 @@
       <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25954,60 +25964,64 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>80.95</v>
+        <v>17.32</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0247</v>
+        <v>0.0058</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>32400</v>
+        <v>12210000</v>
       </c>
       <c r="E588" s="4" t="n">
-        <v>0.58</v>
+        <v>0.9246</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>41.16</v>
-      </c>
-      <c r="G588" s="2" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G588" s="3" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="4" t="n">
-        <v>-9.409700000000001</v>
+        <v>0.0028</v>
       </c>
       <c r="J588" s="4" t="n">
-        <v>-4.155</v>
+        <v>-10.3171</v>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>4.73</v>
+        <v>33.9</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0216</v>
+        <v>-0.0174</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>4590000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>77.90000000000001</v>
+        <v>54.07</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26015,12 +26029,12 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26028,75 +26042,71 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0595</v>
+        <v>0.0247</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>14880000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>32400</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>61.35</v>
+        <v>41.16</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>152.1</v>
+        <v>41.38</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.0222</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>10990000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>52.17</v>
+        <v>60.95</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26104,21 +26114,23 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>16.08</v>
+        <v>4.73</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.0111</v>
+        <v>0.0216</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>72700000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>62450000</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>51.02</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26131,7 +26143,7 @@
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26139,67 +26151,53 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>197.4</v>
+        <v>81.84</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.099</v>
+        <v>0.0027</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>20610000</v>
+        <v>11800000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>45.87</v>
+        <v>45.85</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
       <c r="I593" s="6" t="inlineStr"/>
       <c r="J593" s="6" t="inlineStr"/>
-      <c r="K593" s="6" t="inlineStr">
-        <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+      <c r="K593" s="6" t="inlineStr"/>
+      <c r="L593" s="6" t="inlineStr"/>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>6.95</v>
+        <v>2.82</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0537</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E594" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>263430000</v>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>78.58</v>
+        <v>52.07</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J594" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I594" s="2" t="inlineStr"/>
+      <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26207,7 +26205,7 @@
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26215,239 +26213,227 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>28.66</v>
+        <v>103.5</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0478</v>
+        <v>-0.001</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>18930000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="F595" s="7" t="n">
-        <v>50.42</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
+      <c r="F595" s="6" t="inlineStr"/>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="6" t="inlineStr"/>
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>7.59</v>
+        <v>62.95</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0008</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>477650</v>
+        <v>539710</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>0.95</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>39.58</v>
+        <v>56.09</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
+      <c r="I596" s="2" t="inlineStr"/>
       <c r="J596" s="4" t="n">
-        <v>-0.4678</v>
+        <v>0.4139</v>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr"/>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>103.5</v>
+        <v>13.89</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.0102</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>398550</v>
+        <v>35540000</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
-      <c r="F597" s="6" t="inlineStr"/>
+      <c r="F597" s="7" t="n">
+        <v>54.23</v>
+      </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="6" t="inlineStr"/>
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L597" s="6" t="inlineStr"/>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L597" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>62.95</v>
+        <v>251</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0008</v>
+        <v>-0.0346</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>539710</v>
+        <v>8590</v>
       </c>
       <c r="E598" s="4" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.2578</v>
       </c>
       <c r="F598" s="3" t="n">
-        <v>56.09</v>
+        <v>46.72</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="4" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>2.74</v>
+        <v>6.13</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.0016</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>43.27</v>
+        <v>61.01</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J599" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I599" s="6" t="inlineStr"/>
+      <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
-        </is>
-      </c>
-      <c r="L599" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr"/>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>169</v>
+        <v>7.59</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0236</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E600" s="2" t="inlineStr"/>
+        <v>477650</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F600" s="3" t="n">
-        <v>60.59</v>
+        <v>39.58</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="2" t="inlineStr"/>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="I600" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J600" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>33.9</v>
+        <v>28.66</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0174</v>
+        <v>-0.0478</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>4590000</v>
-      </c>
-      <c r="E601" s="6" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E601" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F601" s="7" t="n">
-        <v>54.07</v>
+        <v>50.42</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
@@ -26455,12 +26441,12 @@
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26501,34 +26487,40 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>39.64</v>
+        <v>2.74</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.0108</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>12770000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>98340000</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>52.02</v>
+        <v>43.27</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26536,48 +26528,62 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>81.84</v>
+        <v>6.95</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>45.85</v>
+        <v>78.58</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="2" t="inlineStr"/>
-      <c r="J604" s="2" t="inlineStr"/>
-      <c r="K604" s="2" t="inlineStr"/>
-      <c r="L604" s="2" t="inlineStr"/>
+      <c r="I604" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J604" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
+      <c r="K604" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>24.62</v>
+        <v>16.08</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0111</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>15600000</v>
+        <v>72700000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>56.05</v>
+        <v>51.02</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26585,12 +26591,12 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26598,21 +26604,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>13.89</v>
+        <v>169</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0102</v>
+        <v>0.0236</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>35540000</v>
+        <v>12070000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>54.23</v>
+        <v>60.59</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26620,12 +26626,12 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26633,42 +26639,40 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>17.32</v>
+        <v>152.1</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0058</v>
+        <v>-0.0225</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>12210000</v>
+        <v>2330000</v>
       </c>
       <c r="E607" s="8" t="n">
-        <v>0.9246</v>
+        <v>0.1071</v>
       </c>
       <c r="F607" s="7" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G607" s="7" t="n">
-        <v>163.71</v>
-      </c>
+        <v>52.17</v>
+      </c>
+      <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="8" t="n">
-        <v>0.0028</v>
+        <v>-3.6635</v>
       </c>
       <c r="J607" s="8" t="n">
-        <v>-10.3171</v>
+        <v>-0.4897</v>
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26695,7 +26699,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 14:38</t>
+          <t>23.04.2026 15:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25824,21 +25824,23 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>197.4</v>
+        <v>28.66</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0478</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>20610000</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>45.87</v>
+        <v>50.42</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25851,7 +25853,7 @@
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25859,21 +25861,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>24.62</v>
+        <v>13.89</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>15600000</v>
+        <v>35540000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>56.05</v>
+        <v>54.23</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25881,12 +25883,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25894,21 +25896,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>41.38</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0595</v>
+        <v>0.0222</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>14880000</v>
+        <v>10990000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>61.35</v>
+        <v>60.95</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25916,12 +25918,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25929,21 +25931,21 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>39.64</v>
+        <v>169</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0236</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>12770000</v>
+        <v>12070000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>52.02</v>
+        <v>60.59</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25951,7 +25953,7 @@
       <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
@@ -25964,42 +25966,32 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>17.32</v>
+        <v>18.99</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0495</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.9246</v>
-      </c>
-      <c r="F588" s="3" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G588" s="3" t="n">
-        <v>163.71</v>
-      </c>
+        <v>102290000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J588" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26007,34 +25999,40 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>33.9</v>
+        <v>6.95</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0174</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>4590000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F589" s="7" t="n">
-        <v>54.07</v>
+        <v>78.58</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
+      <c r="I589" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J589" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26042,157 +26040,161 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>80.95</v>
+        <v>4.73</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0247</v>
+        <v>0.0216</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>32400</v>
+        <v>62450000</v>
       </c>
       <c r="E590" s="4" t="n">
-        <v>0.58</v>
+        <v>0.8667</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>41.16</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>41.38</v>
+        <v>7.59</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0222</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>10990000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>477650</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>60.95</v>
+        <v>39.58</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>4.73</v>
+        <v>81.84</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0027</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>11800000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>45.85</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
       <c r="I592" s="2" t="inlineStr"/>
       <c r="J592" s="2" t="inlineStr"/>
-      <c r="K592" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+      <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="2" t="inlineStr"/>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>81.84</v>
+        <v>62.95</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0027</v>
+        <v>-0.0008</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>45.85</v>
+        <v>56.09</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
       <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
-      <c r="K593" s="6" t="inlineStr"/>
-      <c r="L593" s="6" t="inlineStr"/>
+      <c r="J593" s="8" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="K593" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>2.82</v>
+        <v>197.4</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.099</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>263430000</v>
+        <v>20610000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>52.07</v>
+        <v>45.87</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26200,12 +26202,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26213,67 +26215,83 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>103.5</v>
+        <v>17.32</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.0058</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>398550</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
-      <c r="F595" s="6" t="inlineStr"/>
-      <c r="G595" s="6" t="inlineStr"/>
+        <v>12210000</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="F595" s="7" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="G595" s="7" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
+      <c r="I595" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J595" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>62.95</v>
+        <v>2.74</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0008</v>
+        <v>-0.0108</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>539710</v>
+        <v>98340000</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>56.09</v>
+        <v>43.27</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
       <c r="J596" s="4" t="n">
-        <v>0.4139</v>
+        <v>-0.8093</v>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26281,58 +26299,58 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>13.89</v>
+        <v>80.95</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.0247</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>35540000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>32400</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>54.23</v>
+        <v>41.16</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L597" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L597" s="6" t="inlineStr"/>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>251</v>
+        <v>2.82</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0537</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E598" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>263430000</v>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>46.72</v>
+        <v>52.07</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26340,30 +26358,34 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>6.13</v>
+        <v>16.08</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0111</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>8730000</v>
+        <v>72700000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>61.01</v>
+        <v>51.02</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26374,112 +26396,114 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L599" s="6" t="inlineStr"/>
+      <c r="L599" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>7.59</v>
+        <v>152.1</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0225</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>477650</v>
+        <v>2330000</v>
       </c>
       <c r="E600" s="4" t="n">
-        <v>0.95</v>
+        <v>0.1071</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>39.58</v>
+        <v>52.17</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
       <c r="I600" s="4" t="n">
-        <v>-23.6291</v>
+        <v>-3.6635</v>
       </c>
       <c r="J600" s="4" t="n">
-        <v>-0.4678</v>
+        <v>-0.4897</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr"/>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>28.66</v>
+        <v>103.5</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0478</v>
+        <v>-0.001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>18930000</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="F601" s="7" t="n">
-        <v>50.42</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
+      <c r="F601" s="6" t="inlineStr"/>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr"/>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>18.99</v>
+        <v>33.9</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0495</v>
+        <v>-0.0174</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>102290000</v>
+        <v>4590000</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
-      <c r="F602" s="2" t="inlineStr"/>
+      <c r="F602" s="3" t="n">
+        <v>54.07</v>
+      </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26487,40 +26511,34 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>2.74</v>
+        <v>39.64</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.0195</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>12770000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>43.27</v>
+        <v>52.02</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26528,40 +26546,34 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>6.95</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>75580000</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>14880000</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>78.58</v>
+        <v>61.35</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J604" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I604" s="2" t="inlineStr"/>
+      <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26569,21 +26581,21 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>16.08</v>
+        <v>24.62</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0111</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>72700000</v>
+        <v>15600000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>51.02</v>
+        <v>56.05</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26591,12 +26603,12 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26604,21 +26616,23 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0236</v>
+        <v>-0.0346</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>12070000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>8590</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>60.59</v>
+        <v>46.72</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26626,55 +26640,41 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr"/>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>152.1</v>
+        <v>6.13</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.0016</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>52.17</v>
+        <v>61.01</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 15:30</t>
+          <t>23.04.2026 16:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-04-23.xlsx
+++ b/data/bist_screener_2026-04-23.xlsx
@@ -25824,23 +25824,23 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>28.66</v>
+        <v>251</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0478</v>
+        <v>-0.0346</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>18930000</v>
+        <v>8590</v>
       </c>
       <c r="E584" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.2578</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>50.42</v>
+        <v>46.72</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25848,34 +25848,30 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L584" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L584" s="2" t="inlineStr"/>
       <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>13.89</v>
+        <v>33.9</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.0174</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>35540000</v>
+        <v>4590000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>54.23</v>
+        <v>54.07</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25883,12 +25879,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25896,21 +25892,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>41.38</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0222</v>
+        <v>-0.0595</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>10990000</v>
+        <v>14880000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>60.95</v>
+        <v>61.35</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25918,12 +25914,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25931,67 +25927,67 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>169</v>
+        <v>81.84</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0236</v>
+        <v>0.0027</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>12070000</v>
+        <v>11800000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>60.59</v>
+        <v>45.85</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="6" t="inlineStr"/>
       <c r="J587" s="6" t="inlineStr"/>
-      <c r="K587" s="6" t="inlineStr">
-        <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
-        </is>
-      </c>
+      <c r="K587" s="6" t="inlineStr"/>
+      <c r="L587" s="6" t="inlineStr"/>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>18.99</v>
+        <v>2.74</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0495</v>
+        <v>-0.0108</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>102290000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
-      <c r="F588" s="2" t="inlineStr"/>
+        <v>98340000</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="F588" s="3" t="n">
+        <v>43.27</v>
+      </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="2" t="inlineStr"/>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="I588" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J588" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -25999,32 +25995,28 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>6.95</v>
+        <v>4.73</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0216</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>75580000</v>
+        <v>62450000</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.8667</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>78.58</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J589" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26032,7 +26024,7 @@
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26040,24 +26032,20 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>4.73</v>
+        <v>103.5</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0216</v>
+        <v>-0.001</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>62450000</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="F590" s="3" t="n">
-        <v>77.90000000000001</v>
-      </c>
+        <v>398550</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
+      <c r="F590" s="2" t="inlineStr"/>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
       <c r="I590" s="2" t="inlineStr"/>
@@ -26067,147 +26055,149 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>7.59</v>
+        <v>41.38</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>477650</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>10990000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>39.58</v>
+        <v>60.95</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr"/>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>81.84</v>
+        <v>62.95</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0008</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>539710</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>45.85</v>
+        <v>56.09</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
       <c r="I592" s="2" t="inlineStr"/>
-      <c r="J592" s="2" t="inlineStr"/>
-      <c r="K592" s="2" t="inlineStr"/>
-      <c r="L592" s="2" t="inlineStr"/>
+      <c r="J592" s="4" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="K592" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>62.95</v>
+        <v>7.59</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0008</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>539710</v>
+        <v>477650</v>
       </c>
       <c r="E593" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="F593" s="7" t="n">
-        <v>56.09</v>
+        <v>39.58</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
+      <c r="I593" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
       <c r="J593" s="8" t="n">
-        <v>0.4139</v>
+        <v>-0.4678</v>
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr"/>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>197.4</v>
+        <v>18.99</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0495</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>20610000</v>
+        <v>102290000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
-      <c r="F594" s="3" t="n">
-        <v>45.87</v>
-      </c>
+      <c r="F594" s="2" t="inlineStr"/>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="2" t="inlineStr"/>
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26215,42 +26205,34 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>17.32</v>
+        <v>24.62</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0058</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>15600000</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="G595" s="7" t="n">
-        <v>163.71</v>
-      </c>
+        <v>56.05</v>
+      </c>
+      <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J595" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26258,42 +26240,32 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>2.74</v>
+        <v>6.13</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0108</v>
+        <v>0.0016</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>98340000</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>8730000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>43.27</v>
+        <v>61.01</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J596" s="4" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
@@ -26336,26 +26308,32 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>2.82</v>
+        <v>6.95</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>263430000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>75580000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>52.07</v>
+        <v>78.58</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="I598" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26363,7 +26341,7 @@
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26406,40 +26384,34 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>152.1</v>
+        <v>197.4</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0225</v>
+        <v>-0.099</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>20610000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>52.17</v>
+        <v>45.87</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26447,63 +26419,75 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>103.5</v>
+        <v>39.64</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.001</v>
+        <v>0.0195</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>398550</v>
+        <v>12770000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="6" t="inlineStr"/>
+      <c r="F601" s="7" t="n">
+        <v>52.02</v>
+      </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>33.9</v>
+        <v>152.1</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0225</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>4590000</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
+        <v>2330000</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F602" s="3" t="n">
-        <v>54.07</v>
+        <v>52.17</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26511,21 +26495,21 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>39.64</v>
+        <v>2.82</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0195</v>
+        <v>-0.0537</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>12770000</v>
+        <v>263430000</v>
       </c>
       <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>52.02</v>
+        <v>52.07</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26533,12 +26517,12 @@
       <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26546,21 +26530,21 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>90.84999999999999</v>
+        <v>169</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0595</v>
+        <v>0.0236</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>14880000</v>
+        <v>12070000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>61.35</v>
+        <v>60.59</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26573,7 +26557,7 @@
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26581,21 +26565,23 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>24.62</v>
+        <v>28.66</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0478</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>18930000</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>56.05</v>
+        <v>50.42</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26603,12 +26589,12 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26616,23 +26602,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>251</v>
+        <v>13.89</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0346</v>
+        <v>0.0102</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>8590</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>35540000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>46.72</v>
+        <v>54.23</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26643,38 +26627,54 @@
           <t>İşlenebilen endüstriler</t>
         </is>
       </c>
-      <c r="L606" s="2" t="inlineStr"/>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>6.13</v>
+        <v>17.32</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0016</v>
+        <v>0.0058</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>8730000</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
+        <v>12210000</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F607" s="7" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="G607" s="6" t="inlineStr"/>
+        <v>47.99</v>
+      </c>
+      <c r="G607" s="7" t="n">
+        <v>163.71</v>
+      </c>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>23.04.2026 16:30</t>
+          <t>23.04.2026 16:59</t>
         </is>
       </c>
     </row>
